--- a/public/exports/29188505.xlsx
+++ b/public/exports/29188505.xlsx
@@ -231,16 +231,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2538110</t>
+          <t xml:space="preserve">2539618</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F5">
-        <v>1834</v>
+        <v>481</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -281,16 +281,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2539618</t>
+          <t xml:space="preserve">273337</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F6">
-        <v>481</v>
+        <v>1016</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -331,16 +331,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">5352869</t>
+          <t xml:space="preserve">274342</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F7">
-        <v>662</v>
+        <v>853</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -381,16 +381,16 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">5352869</t>
+          <t xml:space="preserve">274699, 274700</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F8">
-        <v>779</v>
+        <v>2350</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -431,7 +431,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">5356213</t>
+          <t xml:space="preserve">276565</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -440,7 +440,7 @@
         </is>
       </c>
       <c r="F9">
-        <v>428</v>
+        <v>683</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -481,16 +481,16 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">5356675</t>
+          <t xml:space="preserve">5352869</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F10">
-        <v>480</v>
+        <v>662</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -531,16 +531,16 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5369721</t>
+          <t xml:space="preserve">5352869</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F11">
-        <v>1154</v>
+        <v>779</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -581,16 +581,16 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">5374254</t>
+          <t xml:space="preserve">5356213</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F12">
-        <v>850</v>
+        <v>428</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -631,16 +631,16 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">720393, 2512194</t>
+          <t xml:space="preserve">5356675</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F13">
-        <v>3065</v>
+        <v>480</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -681,16 +681,16 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">720398, 2516752</t>
+          <t xml:space="preserve">5374254</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F14">
-        <v>2148</v>
+        <v>850</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">720571, 5357751</t>
+          <t xml:space="preserve">720393, 2512194</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="F15">
-        <v>435</v>
+        <v>3065</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -781,16 +781,16 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">720933, 10220761</t>
+          <t xml:space="preserve">720398, 2516752</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F16">
-        <v>325</v>
+        <v>2148</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">720982, 2509856</t>
+          <t xml:space="preserve">720571, 5357751</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="F17">
-        <v>390</v>
+        <v>435</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -881,16 +881,16 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">720989, 2509860</t>
+          <t xml:space="preserve">720982, 2509856</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F18">
-        <v>2656</v>
+        <v>390</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -936,11 +936,11 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F19">
-        <v>284</v>
+        <v>2656</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -981,16 +981,16 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">721002, 5363768</t>
+          <t xml:space="preserve">720989, 2509860</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F20">
-        <v>254</v>
+        <v>284</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1031,16 +1031,16 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">721004, 2509084</t>
+          <t xml:space="preserve">721002, 5363768</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F21">
-        <v>543</v>
+        <v>254</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1081,16 +1081,16 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">721007, 2509892</t>
+          <t xml:space="preserve">721004, 2509084</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F22">
-        <v>320</v>
+        <v>543</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">721023, 8228900</t>
+          <t xml:space="preserve">721007, 2509892</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="F23">
-        <v>1434</v>
+        <v>320</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">721032, 5370836</t>
+          <t xml:space="preserve">721023, 8228900</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="F24">
-        <v>684</v>
+        <v>1434</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1231,16 +1231,16 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">721034, 5370887</t>
+          <t xml:space="preserve">721032, 5370836</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F25">
-        <v>586</v>
+        <v>684</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1281,16 +1281,16 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">721035, 9364264</t>
+          <t xml:space="preserve">721034, 5370887</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F26">
-        <v>2031</v>
+        <v>586</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1336,11 +1336,11 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F27">
-        <v>550</v>
+        <v>2031</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">721040, 5370710</t>
+          <t xml:space="preserve">721035, 9364264</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F28">
-        <v>289</v>
+        <v>550</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">721044, 5370905</t>
+          <t xml:space="preserve">721040, 5370710</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1440,7 +1440,7 @@
         </is>
       </c>
       <c r="F29">
-        <v>3477</v>
+        <v>289</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">721054, 2534110</t>
+          <t xml:space="preserve">721044, 5370905</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="F30">
-        <v>1637</v>
+        <v>3477</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1531,16 +1531,16 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">721055, 5374101</t>
+          <t xml:space="preserve">721054, 2534110</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F31">
-        <v>702</v>
+        <v>1637</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1581,16 +1581,16 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">721059, 9472289</t>
+          <t xml:space="preserve">721055, 5374101</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F32">
-        <v>1269</v>
+        <v>702</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1781,16 +1781,16 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">8007086</t>
+          <t xml:space="preserve">9375962</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F36">
-        <v>405</v>
+        <v>520</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1831,16 +1831,16 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">9375962</t>
+          <t xml:space="preserve">9599949</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F37">
-        <v>520</v>
+        <v>1389</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1886,11 +1886,11 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F38">
-        <v>1389</v>
+        <v>2939</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1936,11 +1936,11 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F39">
-        <v>2939</v>
+        <v>314</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1981,30 +1981,30 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">9599949</t>
+          <t xml:space="preserve">5364758</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F40">
-        <v>314</v>
+        <v>382</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200044603</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2021-01-20</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2031,35 +2031,35 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">5364758</t>
+          <t xml:space="preserve">721059, 9472289</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F41">
-        <v>382</v>
+        <v>1269</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">200044603</t>
+          <t xml:space="preserve">311269462</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-01-20</t>
+          <t xml:space="preserve">2027-08-29</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311313206</t>
+          <t xml:space="preserve">311313184</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311313207</t>
+          <t xml:space="preserve">311313184</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311313201</t>
+          <t xml:space="preserve">311313184</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3531,20 +3531,20 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">5362593</t>
+          <t xml:space="preserve">8268643</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F71">
-        <v>505</v>
+        <v>790</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311480245</t>
+          <t xml:space="preserve">311480270</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">8268643</t>
+          <t xml:space="preserve">9445550</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3590,16 +3590,16 @@
         </is>
       </c>
       <c r="F72">
-        <v>790</v>
+        <v>1646</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311480270</t>
+          <t xml:space="preserve">311480862</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-03</t>
+          <t xml:space="preserve">2030-12-06</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3631,25 +3631,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">9445550</t>
+          <t xml:space="preserve">9817467</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F73">
-        <v>1646</v>
+        <v>636</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311480862</t>
+          <t xml:space="preserve">311484273</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-06</t>
+          <t xml:space="preserve">2030-12-21</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3681,25 +3681,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440066</t>
+          <t xml:space="preserve">8872440</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F74">
-        <v>693</v>
+        <v>1053</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311481124</t>
+          <t xml:space="preserve">311486475</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-07</t>
+          <t xml:space="preserve">2031-01-08</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3731,25 +3731,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440066</t>
+          <t xml:space="preserve">100008386</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F75">
-        <v>693</v>
+        <v>2040</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311481236</t>
+          <t xml:space="preserve">311487487</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-08</t>
+          <t xml:space="preserve">2031-01-13</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440066</t>
+          <t xml:space="preserve">5370888</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3790,16 +3790,16 @@
         </is>
       </c>
       <c r="F76">
-        <v>882</v>
+        <v>1207</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311481629</t>
+          <t xml:space="preserve">311487360</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-09</t>
+          <t xml:space="preserve">2031-01-13</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3831,25 +3831,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440066</t>
+          <t xml:space="preserve">7182253</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F77">
-        <v>693</v>
+        <v>3047</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311481659</t>
+          <t xml:space="preserve">311487437</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-09</t>
+          <t xml:space="preserve">2031-01-13</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3881,25 +3881,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440066</t>
+          <t xml:space="preserve">2530706</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F78">
-        <v>693</v>
+        <v>407</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311481933</t>
+          <t xml:space="preserve">311487941</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-10</t>
+          <t xml:space="preserve">2031-01-15</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3931,25 +3931,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440066</t>
+          <t xml:space="preserve">5363727</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F79">
-        <v>528</v>
+        <v>3534</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311482005</t>
+          <t xml:space="preserve">311490037</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-10</t>
+          <t xml:space="preserve">2031-01-25</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3981,25 +3981,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440066</t>
+          <t xml:space="preserve">5363727</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F80">
-        <v>677</v>
+        <v>364</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311482315</t>
+          <t xml:space="preserve">311490038</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-11</t>
+          <t xml:space="preserve">2031-01-25</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4031,25 +4031,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440066</t>
+          <t xml:space="preserve">5363727</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F81">
-        <v>714</v>
+        <v>3430</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311482201</t>
+          <t xml:space="preserve">311491016</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-11</t>
+          <t xml:space="preserve">2031-01-28</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4081,25 +4081,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440066</t>
+          <t xml:space="preserve">5363727</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F82">
-        <v>731</v>
+        <v>260</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311482575</t>
+          <t xml:space="preserve">311491019</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-14</t>
+          <t xml:space="preserve">2031-01-28</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4131,25 +4131,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440066</t>
+          <t xml:space="preserve">2517720</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F83">
-        <v>697</v>
+        <v>263</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311482611</t>
+          <t xml:space="preserve">311491922</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-14</t>
+          <t xml:space="preserve">2031-02-01</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4181,25 +4181,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440066</t>
+          <t xml:space="preserve">5363727</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F84">
-        <v>648</v>
+        <v>1072</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311483260</t>
+          <t xml:space="preserve">311492470</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-16</t>
+          <t xml:space="preserve">2031-02-03</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4231,25 +4231,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440066</t>
+          <t xml:space="preserve">9316694</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F85">
-        <v>692</v>
+        <v>2935</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311483927</t>
+          <t xml:space="preserve">311493572</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-18</t>
+          <t xml:space="preserve">2031-02-08</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4281,25 +4281,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">9817467</t>
+          <t xml:space="preserve">2539618</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F86">
-        <v>636</v>
+        <v>2279</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311484273</t>
+          <t xml:space="preserve">311497388</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-21</t>
+          <t xml:space="preserve">2031-02-22</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">8872440</t>
+          <t xml:space="preserve">2516751</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4340,16 +4340,16 @@
         </is>
       </c>
       <c r="F87">
-        <v>1053</v>
+        <v>277</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311486475</t>
+          <t xml:space="preserve">311500800</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-08</t>
+          <t xml:space="preserve">2031-03-05</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4381,25 +4381,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">100008386</t>
+          <t xml:space="preserve">2516403</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F88">
-        <v>2040</v>
+        <v>591</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311487487</t>
+          <t xml:space="preserve">311501345</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-13</t>
+          <t xml:space="preserve">2031-03-08</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4431,25 +4431,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">5370888</t>
+          <t xml:space="preserve">2516403</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F89">
-        <v>1207</v>
+        <v>590</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311487360</t>
+          <t xml:space="preserve">311501407</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-13</t>
+          <t xml:space="preserve">2031-03-08</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4481,25 +4481,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">7182253</t>
+          <t xml:space="preserve">2539618</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F90">
-        <v>3047</v>
+        <v>340</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311487437</t>
+          <t xml:space="preserve">311501290</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-13</t>
+          <t xml:space="preserve">2031-03-08</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4531,25 +4531,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2530706</t>
+          <t xml:space="preserve">2539618</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F91">
-        <v>407</v>
+        <v>277</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311487941</t>
+          <t xml:space="preserve">311501280</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-15</t>
+          <t xml:space="preserve">2031-03-08</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4581,25 +4581,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">5369956</t>
+          <t xml:space="preserve">2513983</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F92">
-        <v>2077</v>
+        <v>1688</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311488996</t>
+          <t xml:space="preserve">311504717</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-20</t>
+          <t xml:space="preserve">2031-03-18</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4631,25 +4631,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">5363727</t>
+          <t xml:space="preserve">100072359</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F93">
-        <v>3534</v>
+        <v>284</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311490037</t>
+          <t xml:space="preserve">311505101</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-25</t>
+          <t xml:space="preserve">2031-03-19</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4681,25 +4681,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">5363727</t>
+          <t xml:space="preserve">5352425</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F94">
-        <v>364</v>
+        <v>395</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311490038</t>
+          <t xml:space="preserve">311505192</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-25</t>
+          <t xml:space="preserve">2031-03-19</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4731,25 +4731,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">5363727</t>
+          <t xml:space="preserve">7961746</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F95">
-        <v>3430</v>
+        <v>722</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311491016</t>
+          <t xml:space="preserve">311504987</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-28</t>
+          <t xml:space="preserve">2031-03-19</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -4781,25 +4781,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">5363727</t>
+          <t xml:space="preserve">9037913</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F96">
-        <v>260</v>
+        <v>452</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311491019</t>
+          <t xml:space="preserve">311506197</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-28</t>
+          <t xml:space="preserve">2031-03-23</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2517720</t>
+          <t xml:space="preserve">5362736</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -4840,16 +4840,16 @@
         </is>
       </c>
       <c r="F97">
-        <v>263</v>
+        <v>327</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311491922</t>
+          <t xml:space="preserve">311506439</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-01</t>
+          <t xml:space="preserve">2031-03-24</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">5363727</t>
+          <t xml:space="preserve">5362459</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -4890,16 +4890,16 @@
         </is>
       </c>
       <c r="F98">
-        <v>1072</v>
+        <v>1312</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311492470</t>
+          <t xml:space="preserve">311506875</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-03</t>
+          <t xml:space="preserve">2031-03-25</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">9316694</t>
+          <t xml:space="preserve">9316745</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -4940,16 +4940,16 @@
         </is>
       </c>
       <c r="F99">
-        <v>2935</v>
+        <v>476</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311493661</t>
+          <t xml:space="preserve">311507001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-08</t>
+          <t xml:space="preserve">2031-03-25</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -4981,25 +4981,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">9364227</t>
+          <t xml:space="preserve">5355644</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F100">
-        <v>1738</v>
+        <v>566</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494209</t>
+          <t xml:space="preserve">311507425</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-10</t>
+          <t xml:space="preserve">2031-03-26</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -5031,25 +5031,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2539618</t>
+          <t xml:space="preserve">100069270</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F101">
-        <v>2279</v>
+        <v>1327</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311497388</t>
+          <t xml:space="preserve">311508092</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-22</t>
+          <t xml:space="preserve">2031-03-29</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2516751</t>
+          <t xml:space="preserve">8525426</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -5090,16 +5090,16 @@
         </is>
       </c>
       <c r="F102">
-        <v>277</v>
+        <v>350</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311500800</t>
+          <t xml:space="preserve">311508001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-05</t>
+          <t xml:space="preserve">2031-03-29</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5131,25 +5131,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2516403</t>
+          <t xml:space="preserve">9508283</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F103">
-        <v>591</v>
+        <v>1358</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311501345</t>
+          <t xml:space="preserve">311508161</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-08</t>
+          <t xml:space="preserve">2031-03-29</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -5181,25 +5181,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2516403</t>
+          <t xml:space="preserve">2539618</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F104">
-        <v>590</v>
+        <v>6548</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311501407</t>
+          <t xml:space="preserve">311508378</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-08</t>
+          <t xml:space="preserve">2031-03-30</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5231,25 +5231,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2539618</t>
+          <t xml:space="preserve">5365177</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F105">
-        <v>340</v>
+        <v>3715</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311501290</t>
+          <t xml:space="preserve">311519707</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-08</t>
+          <t xml:space="preserve">2031-05-12</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5281,25 +5281,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2539618</t>
+          <t xml:space="preserve">5352873</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F106">
-        <v>277</v>
+        <v>2690</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311501280</t>
+          <t xml:space="preserve">311520108</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-08</t>
+          <t xml:space="preserve">2031-05-14</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2513983</t>
+          <t xml:space="preserve">5364701</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -5340,16 +5340,16 @@
         </is>
       </c>
       <c r="F107">
-        <v>1688</v>
+        <v>2349</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311504717</t>
+          <t xml:space="preserve">311520407</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-18</t>
+          <t xml:space="preserve">2031-05-17</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">100072359</t>
+          <t xml:space="preserve">5365401</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -5390,16 +5390,16 @@
         </is>
       </c>
       <c r="F108">
-        <v>284</v>
+        <v>2835</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311505101</t>
+          <t xml:space="preserve">311520408</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-19</t>
+          <t xml:space="preserve">2031-05-17</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">5352425</t>
+          <t xml:space="preserve">2512196</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -5440,16 +5440,16 @@
         </is>
       </c>
       <c r="F109">
-        <v>395</v>
+        <v>2103</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311505192</t>
+          <t xml:space="preserve">311522349</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-19</t>
+          <t xml:space="preserve">2031-05-25</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -5481,25 +5481,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">7961746</t>
+          <t xml:space="preserve">2537303</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F110">
-        <v>722</v>
+        <v>4083</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311504987</t>
+          <t xml:space="preserve">311522700</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-19</t>
+          <t xml:space="preserve">2031-05-26</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -5531,25 +5531,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">9037913</t>
+          <t xml:space="preserve">2537303</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F111">
-        <v>452</v>
+        <v>750</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311506197</t>
+          <t xml:space="preserve">311523579</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-23</t>
+          <t xml:space="preserve">2031-05-28</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">5362736</t>
+          <t xml:space="preserve">5365703</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -5590,16 +5590,16 @@
         </is>
       </c>
       <c r="F112">
-        <v>327</v>
+        <v>2240</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311506439</t>
+          <t xml:space="preserve">311525535</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-24</t>
+          <t xml:space="preserve">2031-06-04</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -5631,25 +5631,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">5362459</t>
+          <t xml:space="preserve">5367460</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F113">
-        <v>1312</v>
+        <v>588</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311506875</t>
+          <t xml:space="preserve">311525848</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-25</t>
+          <t xml:space="preserve">2031-06-07</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">9316745</t>
+          <t xml:space="preserve">9817467</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -5690,16 +5690,16 @@
         </is>
       </c>
       <c r="F114">
-        <v>476</v>
+        <v>3634</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311507001</t>
+          <t xml:space="preserve">311527772</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-25</t>
+          <t xml:space="preserve">2031-06-14</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -5731,25 +5731,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">5355644</t>
+          <t xml:space="preserve">9817467</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F115">
-        <v>566</v>
+        <v>1430</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311507425</t>
+          <t xml:space="preserve">311527791</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-26</t>
+          <t xml:space="preserve">2031-06-14</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">100069270</t>
+          <t xml:space="preserve">5366424</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -5790,16 +5790,16 @@
         </is>
       </c>
       <c r="F116">
-        <v>1327</v>
+        <v>890</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311508092</t>
+          <t xml:space="preserve">311528110</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-29</t>
+          <t xml:space="preserve">2031-06-15</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">8525426</t>
+          <t xml:space="preserve">2510445</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -5844,12 +5844,12 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311508001</t>
+          <t xml:space="preserve">311529584</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-29</t>
+          <t xml:space="preserve">2031-06-21</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">9508283</t>
+          <t xml:space="preserve">2538510</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -5890,16 +5890,16 @@
         </is>
       </c>
       <c r="F118">
-        <v>1358</v>
+        <v>534</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311508161</t>
+          <t xml:space="preserve">311529569</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-29</t>
+          <t xml:space="preserve">2031-06-21</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2539618</t>
+          <t xml:space="preserve">5367674</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -5940,16 +5940,16 @@
         </is>
       </c>
       <c r="F119">
-        <v>6548</v>
+        <v>2009</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311508378</t>
+          <t xml:space="preserve">311530847</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-30</t>
+          <t xml:space="preserve">2031-06-24</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">5365177</t>
+          <t xml:space="preserve">100044819</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -5990,16 +5990,16 @@
         </is>
       </c>
       <c r="F120">
-        <v>3715</v>
+        <v>588</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311519707</t>
+          <t xml:space="preserve">311531573</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-12</t>
+          <t xml:space="preserve">2031-06-28</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">5352873</t>
+          <t xml:space="preserve">5356211</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -6040,16 +6040,16 @@
         </is>
       </c>
       <c r="F121">
-        <v>2690</v>
+        <v>717</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311520108</t>
+          <t xml:space="preserve">311531545</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-14</t>
+          <t xml:space="preserve">2031-06-28</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">5364701</t>
+          <t xml:space="preserve">5369721</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -6090,16 +6090,16 @@
         </is>
       </c>
       <c r="F122">
-        <v>2349</v>
+        <v>1154</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311520407</t>
+          <t xml:space="preserve">311531549</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-17</t>
+          <t xml:space="preserve">2031-06-28</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">5365401</t>
+          <t xml:space="preserve">100037421</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -6140,16 +6140,16 @@
         </is>
       </c>
       <c r="F123">
-        <v>2835</v>
+        <v>382</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311520408</t>
+          <t xml:space="preserve">311532441</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-17</t>
+          <t xml:space="preserve">2031-06-30</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -6181,25 +6181,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2512196</t>
+          <t xml:space="preserve">100037421</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F124">
-        <v>2103</v>
+        <v>301</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311522349</t>
+          <t xml:space="preserve">311532439</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-25</t>
+          <t xml:space="preserve">2031-06-30</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -6231,25 +6231,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2537303</t>
+          <t xml:space="preserve">2510023</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F125">
-        <v>4083</v>
+        <v>755</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311522700</t>
+          <t xml:space="preserve">311532382</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-26</t>
+          <t xml:space="preserve">2031-06-30</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -6281,25 +6281,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2537303</t>
+          <t xml:space="preserve">5366539</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F126">
-        <v>750</v>
+        <v>957</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311523579</t>
+          <t xml:space="preserve">311532388</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-28</t>
+          <t xml:space="preserve">2031-06-30</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">5365703</t>
+          <t xml:space="preserve">2538114</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -6340,16 +6340,16 @@
         </is>
       </c>
       <c r="F127">
-        <v>2240</v>
+        <v>270</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311525535</t>
+          <t xml:space="preserve">311532763</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-04</t>
+          <t xml:space="preserve">2031-07-01</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -6381,25 +6381,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">5367460</t>
+          <t xml:space="preserve">2538114</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F128">
-        <v>588</v>
+        <v>367</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311525861</t>
+          <t xml:space="preserve">311532763</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-07</t>
+          <t xml:space="preserve">2031-07-01</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -6431,25 +6431,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">9817467</t>
+          <t xml:space="preserve">5366711</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F129">
-        <v>3634</v>
+        <v>307</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311527772</t>
+          <t xml:space="preserve">311539234</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-14</t>
+          <t xml:space="preserve">2031-08-05</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -6481,25 +6481,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">9817467</t>
+          <t xml:space="preserve">5366711</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F130">
-        <v>1430</v>
+        <v>1748</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311527791</t>
+          <t xml:space="preserve">311539376</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-14</t>
+          <t xml:space="preserve">2031-08-06</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -6531,25 +6531,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">5366424</t>
+          <t xml:space="preserve">5366711</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F131">
-        <v>890</v>
+        <v>1479</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311528110</t>
+          <t xml:space="preserve">311539398</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-15</t>
+          <t xml:space="preserve">2031-08-06</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2510445</t>
+          <t xml:space="preserve">2516403</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -6590,16 +6590,16 @@
         </is>
       </c>
       <c r="F132">
-        <v>350</v>
+        <v>3007</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311529584</t>
+          <t xml:space="preserve">311539671</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-21</t>
+          <t xml:space="preserve">2031-08-09</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -6631,7 +6631,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2538510</t>
+          <t xml:space="preserve">5366711</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -6640,16 +6640,16 @@
         </is>
       </c>
       <c r="F133">
-        <v>534</v>
+        <v>3351</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311529569</t>
+          <t xml:space="preserve">311539622</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-21</t>
+          <t xml:space="preserve">2031-08-09</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -6681,25 +6681,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">5367674</t>
+          <t xml:space="preserve">5366711</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F134">
-        <v>2009</v>
+        <v>2511</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311530847</t>
+          <t xml:space="preserve">311539622</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-24</t>
+          <t xml:space="preserve">2031-08-09</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -6731,25 +6731,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">100044819</t>
+          <t xml:space="preserve">5366711</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F135">
-        <v>588</v>
+        <v>1140</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311531573</t>
+          <t xml:space="preserve">311539622</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-28</t>
+          <t xml:space="preserve">2031-08-09</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">5356211</t>
+          <t xml:space="preserve">5372045</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -6790,16 +6790,16 @@
         </is>
       </c>
       <c r="F136">
-        <v>717</v>
+        <v>1205</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311531545</t>
+          <t xml:space="preserve">311539841</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-28</t>
+          <t xml:space="preserve">2031-08-10</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -6831,25 +6831,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">100037421</t>
+          <t xml:space="preserve">5372045</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F137">
-        <v>382</v>
+        <v>1120</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311532441</t>
+          <t xml:space="preserve">311540151</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-30</t>
+          <t xml:space="preserve">2031-08-11</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -6881,25 +6881,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">100037421</t>
+          <t xml:space="preserve">5365298</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F138">
-        <v>301</v>
+        <v>1409</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311532439</t>
+          <t xml:space="preserve">311540403</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-30</t>
+          <t xml:space="preserve">2031-08-12</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2510023</t>
+          <t xml:space="preserve">2509084</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -6940,16 +6940,16 @@
         </is>
       </c>
       <c r="F139">
-        <v>755</v>
+        <v>338</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311532382</t>
+          <t xml:space="preserve">311541914</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-30</t>
+          <t xml:space="preserve">2031-08-19</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -6981,25 +6981,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">5366539</t>
+          <t xml:space="preserve">5372045</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F140">
-        <v>957</v>
+        <v>4812</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311532388</t>
+          <t xml:space="preserve">311542201</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-30</t>
+          <t xml:space="preserve">2031-08-20</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -7031,25 +7031,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2538114</t>
+          <t xml:space="preserve">5372045</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F141">
-        <v>270</v>
+        <v>1061</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311532763</t>
+          <t xml:space="preserve">311542780</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-01</t>
+          <t xml:space="preserve">2031-08-24</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -7081,25 +7081,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2538114</t>
+          <t xml:space="preserve">5372045</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F142">
-        <v>367</v>
+        <v>4921</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311532763</t>
+          <t xml:space="preserve">311543723</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-01</t>
+          <t xml:space="preserve">2031-08-27</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -7131,25 +7131,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">5366711</t>
+          <t xml:space="preserve">5372045</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F143">
-        <v>307</v>
+        <v>531</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539234</t>
+          <t xml:space="preserve">311544102</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-05</t>
+          <t xml:space="preserve">2031-08-30</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -7181,25 +7181,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">5366711</t>
+          <t xml:space="preserve">5372045</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F144">
-        <v>1748</v>
+        <v>550</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539376</t>
+          <t xml:space="preserve">311544121</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-06</t>
+          <t xml:space="preserve">2031-08-30</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -7231,25 +7231,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">5366711</t>
+          <t xml:space="preserve">5372045</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F145">
-        <v>1479</v>
+        <v>2205</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539398</t>
+          <t xml:space="preserve">311544116</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-06</t>
+          <t xml:space="preserve">2031-08-30</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -7281,7 +7281,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2516403</t>
+          <t xml:space="preserve">5354432</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -7290,16 +7290,16 @@
         </is>
       </c>
       <c r="F146">
-        <v>3007</v>
+        <v>1732</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539671</t>
+          <t xml:space="preserve">311544586</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-09</t>
+          <t xml:space="preserve">2031-08-31</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">5366711</t>
+          <t xml:space="preserve">100039122</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -7340,16 +7340,16 @@
         </is>
       </c>
       <c r="F147">
-        <v>3351</v>
+        <v>1603</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539622</t>
+          <t xml:space="preserve">311546941</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-09</t>
+          <t xml:space="preserve">2031-09-09</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -7381,25 +7381,25 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">5366711</t>
+          <t xml:space="preserve">2509761</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F148">
-        <v>2511</v>
+        <v>347</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539622</t>
+          <t xml:space="preserve">311547259</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-09</t>
+          <t xml:space="preserve">2031-09-10</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -7431,25 +7431,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">5366711</t>
+          <t xml:space="preserve">2509761</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F149">
-        <v>1140</v>
+        <v>1684</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539622</t>
+          <t xml:space="preserve">311547259</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-09</t>
+          <t xml:space="preserve">2031-09-10</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -7481,25 +7481,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">5372045</t>
+          <t xml:space="preserve">2509761</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F150">
-        <v>1205</v>
+        <v>412</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539841</t>
+          <t xml:space="preserve">311547259</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-10</t>
+          <t xml:space="preserve">2031-09-10</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -7531,25 +7531,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">5372045</t>
+          <t xml:space="preserve">2509761</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="F151">
-        <v>1120</v>
+        <v>672</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311540151</t>
+          <t xml:space="preserve">311547259</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-11</t>
+          <t xml:space="preserve">2031-09-10</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -7581,25 +7581,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">5365298</t>
+          <t xml:space="preserve">2509761</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="F152">
-        <v>1409</v>
+        <v>1564</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311540403</t>
+          <t xml:space="preserve">311547259</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-12</t>
+          <t xml:space="preserve">2031-09-10</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -7631,25 +7631,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509084</t>
+          <t xml:space="preserve">2509761</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F153">
-        <v>338</v>
+        <v>251</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311541914</t>
+          <t xml:space="preserve">311547259</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-19</t>
+          <t xml:space="preserve">2031-09-10</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -7681,25 +7681,25 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">5372045</t>
+          <t xml:space="preserve">5365179</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F154">
-        <v>4812</v>
+        <v>1527</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311542201</t>
+          <t xml:space="preserve">311547442</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-20</t>
+          <t xml:space="preserve">2031-09-10</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -7731,25 +7731,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">5372045</t>
+          <t xml:space="preserve">5367350</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F155">
-        <v>1061</v>
+        <v>2616</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311542780</t>
+          <t xml:space="preserve">311547289</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-24</t>
+          <t xml:space="preserve">2031-09-10</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -7781,25 +7781,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">5372045</t>
+          <t xml:space="preserve">2509761</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F156">
-        <v>4921</v>
+        <v>4519</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311543723</t>
+          <t xml:space="preserve">311547586</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-27</t>
+          <t xml:space="preserve">2031-09-13</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -7831,25 +7831,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">5372045</t>
+          <t xml:space="preserve">2509890</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F157">
-        <v>531</v>
+        <v>622</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311544102</t>
+          <t xml:space="preserve">311547660</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-30</t>
+          <t xml:space="preserve">2031-09-13</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -7881,25 +7881,25 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">5372045</t>
+          <t xml:space="preserve">2509890</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F158">
-        <v>550</v>
+        <v>461</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311544121</t>
+          <t xml:space="preserve">311547618</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-30</t>
+          <t xml:space="preserve">2031-09-13</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -7931,25 +7931,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">5372045</t>
+          <t xml:space="preserve">5352869</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F159">
-        <v>2205</v>
+        <v>3202</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311544116</t>
+          <t xml:space="preserve">311547605</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-30</t>
+          <t xml:space="preserve">2031-09-13</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -7981,25 +7981,25 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509761</t>
+          <t xml:space="preserve">5363800</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F160">
-        <v>1684</v>
+        <v>364</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311544591</t>
+          <t xml:space="preserve">311547930</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-31</t>
+          <t xml:space="preserve">2031-09-14</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">274342</t>
+          <t xml:space="preserve">5371082</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -8040,16 +8040,16 @@
         </is>
       </c>
       <c r="F161">
-        <v>853</v>
+        <v>1244</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311544492</t>
+          <t xml:space="preserve">311548237</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-31</t>
+          <t xml:space="preserve">2031-09-15</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -8081,25 +8081,25 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">5354432</t>
+          <t xml:space="preserve">5373175</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F162">
-        <v>1732</v>
+        <v>874</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311544586</t>
+          <t xml:space="preserve">311548621</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-31</t>
+          <t xml:space="preserve">2031-09-16</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -8131,25 +8131,25 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509761</t>
+          <t xml:space="preserve">5353043</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F163">
-        <v>672</v>
+        <v>1638</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311545069</t>
+          <t xml:space="preserve">311549963</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-01</t>
+          <t xml:space="preserve">2031-09-22</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -8181,25 +8181,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509761</t>
+          <t xml:space="preserve">2539906</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F164">
-        <v>412</v>
+        <v>293</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311545259</t>
+          <t xml:space="preserve">311550259</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-02</t>
+          <t xml:space="preserve">2031-09-23</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -8231,25 +8231,25 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509761</t>
+          <t xml:space="preserve">2529964</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F165">
-        <v>251</v>
+        <v>691</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311546548</t>
+          <t xml:space="preserve">311550899</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-08</t>
+          <t xml:space="preserve">2031-09-27</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -8281,25 +8281,25 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">100039122</t>
+          <t xml:space="preserve">2529964</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F166">
-        <v>1603</v>
+        <v>582</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311546941</t>
+          <t xml:space="preserve">311550940</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-09</t>
+          <t xml:space="preserve">2031-09-27</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -8331,25 +8331,25 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509761</t>
+          <t xml:space="preserve">2529964</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F167">
-        <v>1564</v>
+        <v>665</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311546897</t>
+          <t xml:space="preserve">311550949</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-09</t>
+          <t xml:space="preserve">2031-09-27</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -8381,25 +8381,25 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509761</t>
+          <t xml:space="preserve">2539906</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F168">
-        <v>347</v>
+        <v>262</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547265</t>
+          <t xml:space="preserve">311551144</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-10</t>
+          <t xml:space="preserve">2031-09-27</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -8431,25 +8431,25 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">5365179</t>
+          <t xml:space="preserve">2539906</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F169">
-        <v>1527</v>
+        <v>262</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547442</t>
+          <t xml:space="preserve">311551144</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-10</t>
+          <t xml:space="preserve">2031-09-27</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -8481,25 +8481,25 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">5367350</t>
+          <t xml:space="preserve">2539906</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F170">
-        <v>2616</v>
+        <v>302</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547289</t>
+          <t xml:space="preserve">311551144</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-10</t>
+          <t xml:space="preserve">2031-09-27</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -8531,25 +8531,25 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509761</t>
+          <t xml:space="preserve">2539906</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F171">
-        <v>4519</v>
+        <v>302</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547586</t>
+          <t xml:space="preserve">311551144</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-13</t>
+          <t xml:space="preserve">2031-09-27</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -8581,25 +8581,25 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509890</t>
+          <t xml:space="preserve">2539906</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F172">
-        <v>622</v>
+        <v>262</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547660</t>
+          <t xml:space="preserve">311551144</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-13</t>
+          <t xml:space="preserve">2031-09-27</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -8631,25 +8631,25 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509890</t>
+          <t xml:space="preserve">9848819</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F173">
-        <v>461</v>
+        <v>1668</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547618</t>
+          <t xml:space="preserve">311551003</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-13</t>
+          <t xml:space="preserve">2031-09-27</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -8681,25 +8681,25 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t xml:space="preserve">5352869</t>
+          <t xml:space="preserve">5355580</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F174">
-        <v>3202</v>
+        <v>564</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547605</t>
+          <t xml:space="preserve">311551302</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-13</t>
+          <t xml:space="preserve">2031-09-28</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -8731,25 +8731,25 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t xml:space="preserve">5363800</t>
+          <t xml:space="preserve">5355580</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F175">
-        <v>364</v>
+        <v>280</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547982</t>
+          <t xml:space="preserve">311551303</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-14</t>
+          <t xml:space="preserve">2031-09-28</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -8781,25 +8781,25 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t xml:space="preserve">5371082</t>
+          <t xml:space="preserve">9599949</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F176">
-        <v>1244</v>
+        <v>660</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311548237</t>
+          <t xml:space="preserve">311552088</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-15</t>
+          <t xml:space="preserve">2031-09-30</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -8831,25 +8831,25 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">5373175</t>
+          <t xml:space="preserve">9223561</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F177">
-        <v>874</v>
+        <v>1762</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311548621</t>
+          <t xml:space="preserve">311554266</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-16</t>
+          <t xml:space="preserve">2031-10-11</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -8881,25 +8881,25 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t xml:space="preserve">5353043</t>
+          <t xml:space="preserve">9223561</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F178">
-        <v>1638</v>
+        <v>1458</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549963</t>
+          <t xml:space="preserve">311554279</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-22</t>
+          <t xml:space="preserve">2031-10-11</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -8931,25 +8931,25 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2539906</t>
+          <t xml:space="preserve">5353438</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F179">
-        <v>293</v>
+        <v>4163</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311550259</t>
+          <t xml:space="preserve">311556144</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-23</t>
+          <t xml:space="preserve">2031-10-19</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -8981,25 +8981,25 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2529964</t>
+          <t xml:space="preserve">5353438</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F180">
-        <v>691</v>
+        <v>1262</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311550899</t>
+          <t xml:space="preserve">311556454</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-27</t>
+          <t xml:space="preserve">2031-10-20</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -9031,25 +9031,25 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2529964</t>
+          <t xml:space="preserve">5353438</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F181">
-        <v>582</v>
+        <v>2360</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311550940</t>
+          <t xml:space="preserve">311558566</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-27</t>
+          <t xml:space="preserve">2031-10-29</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -9081,25 +9081,25 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2529964</t>
+          <t xml:space="preserve">10041598</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F182">
-        <v>665</v>
+        <v>294</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311550949</t>
+          <t xml:space="preserve">311558916</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-27</t>
+          <t xml:space="preserve">2031-11-01</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -9131,7 +9131,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2539906</t>
+          <t xml:space="preserve">5364982</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -9140,16 +9140,16 @@
         </is>
       </c>
       <c r="F183">
-        <v>262</v>
+        <v>1101</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311551144</t>
+          <t xml:space="preserve">311558955</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-27</t>
+          <t xml:space="preserve">2031-11-01</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -9181,7 +9181,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2539906</t>
+          <t xml:space="preserve">5364982</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -9190,16 +9190,16 @@
         </is>
       </c>
       <c r="F184">
-        <v>262</v>
+        <v>1512</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311551144</t>
+          <t xml:space="preserve">311558978</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-27</t>
+          <t xml:space="preserve">2031-11-01</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -9231,25 +9231,25 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2539906</t>
+          <t xml:space="preserve">5367089</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F185">
-        <v>302</v>
+        <v>1770</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311551144</t>
+          <t xml:space="preserve">311558842</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-27</t>
+          <t xml:space="preserve">2031-11-01</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2539906</t>
+          <t xml:space="preserve">5367089</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -9290,16 +9290,16 @@
         </is>
       </c>
       <c r="F186">
-        <v>302</v>
+        <v>561</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311551144</t>
+          <t xml:space="preserve">311558830</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-27</t>
+          <t xml:space="preserve">2031-11-01</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -9331,25 +9331,25 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2539906</t>
+          <t xml:space="preserve">5355259</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F187">
-        <v>262</v>
+        <v>3102</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311551144</t>
+          <t xml:space="preserve">311559245</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-27</t>
+          <t xml:space="preserve">2031-11-02</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -9381,25 +9381,25 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t xml:space="preserve">9848819</t>
+          <t xml:space="preserve">5364982</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F188">
-        <v>1668</v>
+        <v>1246</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311551003</t>
+          <t xml:space="preserve">311559093</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-27</t>
+          <t xml:space="preserve">2031-11-02</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -9431,25 +9431,25 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t xml:space="preserve">5355580</t>
+          <t xml:space="preserve">10041598</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F189">
-        <v>564</v>
+        <v>1218</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311551302</t>
+          <t xml:space="preserve">311559440</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-28</t>
+          <t xml:space="preserve">2031-11-03</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -9481,25 +9481,25 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t xml:space="preserve">5355580</t>
+          <t xml:space="preserve">8063257</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F190">
-        <v>280</v>
+        <v>1167</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311551303</t>
+          <t xml:space="preserve">311559529</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-28</t>
+          <t xml:space="preserve">2031-11-03</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -9531,25 +9531,25 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t xml:space="preserve">9599949</t>
+          <t xml:space="preserve">100051113</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F191">
-        <v>660</v>
+        <v>902</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311552088</t>
+          <t xml:space="preserve">311560219</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-30</t>
+          <t xml:space="preserve">2031-11-08</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t xml:space="preserve">9223561</t>
+          <t xml:space="preserve">5372069</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -9590,16 +9590,16 @@
         </is>
       </c>
       <c r="F192">
-        <v>1762</v>
+        <v>735</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311554266</t>
+          <t xml:space="preserve">311561231</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-11</t>
+          <t xml:space="preserve">2031-11-11</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -9631,25 +9631,25 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t xml:space="preserve">9223561</t>
+          <t xml:space="preserve">5372069</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F193">
-        <v>1458</v>
+        <v>266</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311554279</t>
+          <t xml:space="preserve">311561278</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-11</t>
+          <t xml:space="preserve">2031-11-11</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -9681,7 +9681,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t xml:space="preserve">5353438</t>
+          <t xml:space="preserve">100048065</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -9690,16 +9690,16 @@
         </is>
       </c>
       <c r="F194">
-        <v>4163</v>
+        <v>754</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311556144</t>
+          <t xml:space="preserve">311562131</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-19</t>
+          <t xml:space="preserve">2031-11-16</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -9731,25 +9731,25 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t xml:space="preserve">5353438</t>
+          <t xml:space="preserve">100048065</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F195">
-        <v>1262</v>
+        <v>754</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311556454</t>
+          <t xml:space="preserve">311562133</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-20</t>
+          <t xml:space="preserve">2031-11-16</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -9781,25 +9781,25 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t xml:space="preserve">5353438</t>
+          <t xml:space="preserve">5353802</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F196">
-        <v>2360</v>
+        <v>1229</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558566</t>
+          <t xml:space="preserve">311564825</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-29</t>
+          <t xml:space="preserve">2031-11-29</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -9831,7 +9831,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t xml:space="preserve">10041598</t>
+          <t xml:space="preserve">5353802</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -9840,16 +9840,16 @@
         </is>
       </c>
       <c r="F197">
-        <v>294</v>
+        <v>1839</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558916</t>
+          <t xml:space="preserve">311564831</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-01</t>
+          <t xml:space="preserve">2031-11-29</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -9881,25 +9881,25 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t xml:space="preserve">5364982</t>
+          <t xml:space="preserve">5353802</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F198">
-        <v>1101</v>
+        <v>686</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558955</t>
+          <t xml:space="preserve">311564875</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-01</t>
+          <t xml:space="preserve">2031-11-29</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -9931,25 +9931,25 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t xml:space="preserve">5364982</t>
+          <t xml:space="preserve">5353802</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F199">
-        <v>1512</v>
+        <v>590</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558978</t>
+          <t xml:space="preserve">311564886</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-01</t>
+          <t xml:space="preserve">2031-11-29</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -9981,7 +9981,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t xml:space="preserve">5367089</t>
+          <t xml:space="preserve">5362905</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -9990,16 +9990,16 @@
         </is>
       </c>
       <c r="F200">
-        <v>1770</v>
+        <v>3290</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558846</t>
+          <t xml:space="preserve">311565082</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-01</t>
+          <t xml:space="preserve">2031-11-30</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -10031,25 +10031,25 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t xml:space="preserve">5367089</t>
+          <t xml:space="preserve">5352531</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F201">
-        <v>561</v>
+        <v>1914</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558830</t>
+          <t xml:space="preserve">311566473</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-01</t>
+          <t xml:space="preserve">2031-12-07</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -10081,7 +10081,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t xml:space="preserve">5355259</t>
+          <t xml:space="preserve">5367901</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -10090,16 +10090,16 @@
         </is>
       </c>
       <c r="F202">
-        <v>3102</v>
+        <v>3906</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311559245</t>
+          <t xml:space="preserve">311566457</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-02</t>
+          <t xml:space="preserve">2031-12-07</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -10131,25 +10131,25 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t xml:space="preserve">5364982</t>
+          <t xml:space="preserve">5367901</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F203">
-        <v>1246</v>
+        <v>1443</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311559093</t>
+          <t xml:space="preserve">311566459</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-02</t>
+          <t xml:space="preserve">2031-12-07</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t xml:space="preserve">10041598</t>
+          <t xml:space="preserve">7900308</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -10190,16 +10190,16 @@
         </is>
       </c>
       <c r="F204">
-        <v>1218</v>
+        <v>455</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311559440</t>
+          <t xml:space="preserve">311567544</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-03</t>
+          <t xml:space="preserve">2031-12-13</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -10231,25 +10231,25 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t xml:space="preserve">8063257</t>
+          <t xml:space="preserve">5372195</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F205">
-        <v>1167</v>
+        <v>432</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t xml:space="preserve">311559529</t>
+          <t xml:space="preserve">311569003</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-03</t>
+          <t xml:space="preserve">2031-12-20</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -10281,25 +10281,25 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t xml:space="preserve">100051113</t>
+          <t xml:space="preserve">5372195</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F206">
-        <v>902</v>
+        <v>680</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560225</t>
+          <t xml:space="preserve">311568956</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-08</t>
+          <t xml:space="preserve">2031-12-20</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -10331,25 +10331,25 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440066</t>
+          <t xml:space="preserve">5372195</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F207">
-        <v>296</v>
+        <v>425</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560825</t>
+          <t xml:space="preserve">311568977</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-10</t>
+          <t xml:space="preserve">2031-12-20</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t xml:space="preserve">5372069</t>
+          <t xml:space="preserve">5372195</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -10390,16 +10390,16 @@
         </is>
       </c>
       <c r="F208">
-        <v>735</v>
+        <v>2423</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311561231</t>
+          <t xml:space="preserve">311569315</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-11</t>
+          <t xml:space="preserve">2031-12-21</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -10431,25 +10431,25 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t xml:space="preserve">5372069</t>
+          <t xml:space="preserve">5372195</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F209">
-        <v>266</v>
+        <v>655</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311561278</t>
+          <t xml:space="preserve">311569344</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-11</t>
+          <t xml:space="preserve">2031-12-21</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t xml:space="preserve">100048065</t>
+          <t xml:space="preserve">2532379</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -10490,16 +10490,16 @@
         </is>
       </c>
       <c r="F210">
-        <v>754</v>
+        <v>856</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562131</t>
+          <t xml:space="preserve">311569765</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-16</t>
+          <t xml:space="preserve">2031-12-23</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -10531,25 +10531,25 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t xml:space="preserve">100048065</t>
+          <t xml:space="preserve">2532379</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F211">
-        <v>754</v>
+        <v>574</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562138</t>
+          <t xml:space="preserve">311569773</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-16</t>
+          <t xml:space="preserve">2031-12-23</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -10581,7 +10581,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t xml:space="preserve">5353802</t>
+          <t xml:space="preserve">5369490</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -10590,16 +10590,16 @@
         </is>
       </c>
       <c r="F212">
-        <v>1229</v>
+        <v>553</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311564825</t>
+          <t xml:space="preserve">311569796</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-29</t>
+          <t xml:space="preserve">2031-12-23</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -10631,25 +10631,25 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t xml:space="preserve">5353802</t>
+          <t xml:space="preserve">5369490</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F213">
-        <v>1839</v>
+        <v>367</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311564831</t>
+          <t xml:space="preserve">311569796</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-29</t>
+          <t xml:space="preserve">2031-12-23</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -10681,25 +10681,25 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t xml:space="preserve">5353802</t>
+          <t xml:space="preserve">9364227</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F214">
-        <v>686</v>
+        <v>1738</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311564875</t>
+          <t xml:space="preserve">311570292</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-29</t>
+          <t xml:space="preserve">2032-01-03</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -10731,25 +10731,25 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t xml:space="preserve">5353802</t>
+          <t xml:space="preserve">2532420</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F215">
-        <v>590</v>
+        <v>5003</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311564886</t>
+          <t xml:space="preserve">311570736</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-29</t>
+          <t xml:space="preserve">2032-01-05</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -10781,25 +10781,25 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t xml:space="preserve">5362905</t>
+          <t xml:space="preserve">2510279</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F216">
-        <v>3290</v>
+        <v>369</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t xml:space="preserve">311565082</t>
+          <t xml:space="preserve">311571117</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-30</t>
+          <t xml:space="preserve">2032-01-07</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -10831,25 +10831,25 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t xml:space="preserve">5352531</t>
+          <t xml:space="preserve">2510279</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F217">
-        <v>1914</v>
+        <v>296</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311566478</t>
+          <t xml:space="preserve">311571117</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-07</t>
+          <t xml:space="preserve">2032-01-07</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -10881,7 +10881,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t xml:space="preserve">5367901</t>
+          <t xml:space="preserve">2515317</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -10890,16 +10890,16 @@
         </is>
       </c>
       <c r="F218">
-        <v>3906</v>
+        <v>290</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311566457</t>
+          <t xml:space="preserve">311571924</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-07</t>
+          <t xml:space="preserve">2032-01-12</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -10931,25 +10931,25 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t xml:space="preserve">5367901</t>
+          <t xml:space="preserve">5372195</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F219">
-        <v>1443</v>
+        <v>2115</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t xml:space="preserve">311566459</t>
+          <t xml:space="preserve">311572013</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-07</t>
+          <t xml:space="preserve">2032-01-12</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -10981,25 +10981,25 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t xml:space="preserve">7900308</t>
+          <t xml:space="preserve">5372195</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F220">
-        <v>455</v>
+        <v>1513</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t xml:space="preserve">311567544</t>
+          <t xml:space="preserve">311572023</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-13</t>
+          <t xml:space="preserve">2032-01-12</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -11031,7 +11031,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t xml:space="preserve">100054057</t>
+          <t xml:space="preserve">2510166</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -11040,16 +11040,16 @@
         </is>
       </c>
       <c r="F221">
-        <v>728</v>
+        <v>3182</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t xml:space="preserve">311567760</t>
+          <t xml:space="preserve">311572673</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-14</t>
+          <t xml:space="preserve">2032-01-17</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -11081,25 +11081,25 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t xml:space="preserve">100054057</t>
+          <t xml:space="preserve">5372017</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F222">
-        <v>1718</v>
+        <v>2825</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t xml:space="preserve">311567765</t>
+          <t xml:space="preserve">311573634</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-14</t>
+          <t xml:space="preserve">2032-01-20</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -11131,25 +11131,25 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t xml:space="preserve">100054057</t>
+          <t xml:space="preserve">1321129</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F223">
-        <v>1718</v>
+        <v>260</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t xml:space="preserve">311567765</t>
+          <t xml:space="preserve">311573835</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-14</t>
+          <t xml:space="preserve">2032-01-21</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -11181,25 +11181,25 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t xml:space="preserve">100054057</t>
+          <t xml:space="preserve">1321129</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F224">
-        <v>3496</v>
+        <v>256</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t xml:space="preserve">311567772</t>
+          <t xml:space="preserve">311573835</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-14</t>
+          <t xml:space="preserve">2032-01-21</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -11231,25 +11231,25 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t xml:space="preserve">100054057</t>
+          <t xml:space="preserve">1321129</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F225">
-        <v>3496</v>
+        <v>285</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t xml:space="preserve">311567777</t>
+          <t xml:space="preserve">311573835</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-14</t>
+          <t xml:space="preserve">2032-01-21</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -11281,25 +11281,25 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t xml:space="preserve">5372195</t>
+          <t xml:space="preserve">5356675</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F226">
-        <v>432</v>
+        <v>2434</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t xml:space="preserve">311569003</t>
+          <t xml:space="preserve">311573780</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-20</t>
+          <t xml:space="preserve">2032-01-21</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -11331,25 +11331,25 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t xml:space="preserve">5372195</t>
+          <t xml:space="preserve">1321129</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F227">
-        <v>680</v>
+        <v>271</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568956</t>
+          <t xml:space="preserve">311574234</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-20</t>
+          <t xml:space="preserve">2032-01-24</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -11381,25 +11381,25 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t xml:space="preserve">5372195</t>
+          <t xml:space="preserve">2538110</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F228">
-        <v>425</v>
+        <v>1834</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568977</t>
+          <t xml:space="preserve">311577742</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-20</t>
+          <t xml:space="preserve">2032-02-09</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -11431,25 +11431,25 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t xml:space="preserve">5372195</t>
+          <t xml:space="preserve">5369956</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F229">
-        <v>2423</v>
+        <v>678</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t xml:space="preserve">311569315</t>
+          <t xml:space="preserve">311579598</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-21</t>
+          <t xml:space="preserve">2032-02-18</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -11481,25 +11481,25 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t xml:space="preserve">5372195</t>
+          <t xml:space="preserve">5369956</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F230">
-        <v>655</v>
+        <v>2077</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t xml:space="preserve">311569344</t>
+          <t xml:space="preserve">311579646</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-21</t>
+          <t xml:space="preserve">2032-02-18</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -11531,25 +11531,25 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t xml:space="preserve">5369490</t>
+          <t xml:space="preserve">5369956</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F231">
-        <v>553</v>
+        <v>814</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t xml:space="preserve">311569560</t>
+          <t xml:space="preserve">311579613</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-22</t>
+          <t xml:space="preserve">2032-02-18</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -11581,7 +11581,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t xml:space="preserve">2532379</t>
+          <t xml:space="preserve">5364595</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -11590,16 +11590,16 @@
         </is>
       </c>
       <c r="F232">
-        <v>856</v>
+        <v>790</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311569765</t>
+          <t xml:space="preserve">311584819</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-23</t>
+          <t xml:space="preserve">2032-03-14</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -11631,7 +11631,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t xml:space="preserve">2532379</t>
+          <t xml:space="preserve">5364595</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -11640,16 +11640,16 @@
         </is>
       </c>
       <c r="F233">
-        <v>574</v>
+        <v>1676</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t xml:space="preserve">311569773</t>
+          <t xml:space="preserve">311585992</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-23</t>
+          <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -11681,25 +11681,25 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t xml:space="preserve">5369490</t>
+          <t xml:space="preserve">5369956</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F234">
-        <v>367</v>
+        <v>2450</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t xml:space="preserve">311569852</t>
+          <t xml:space="preserve">311588963</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-23</t>
+          <t xml:space="preserve">2032-03-29</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t xml:space="preserve">2532420</t>
+          <t xml:space="preserve">5369956</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -11740,16 +11740,16 @@
         </is>
       </c>
       <c r="F235">
-        <v>5003</v>
+        <v>1827</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t xml:space="preserve">311570736</t>
+          <t xml:space="preserve">311589574</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-05</t>
+          <t xml:space="preserve">2032-03-31</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -11781,25 +11781,25 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t xml:space="preserve">2510279</t>
+          <t xml:space="preserve">5369956</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F236">
-        <v>369</v>
+        <v>1031</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t xml:space="preserve">311570962</t>
+          <t xml:space="preserve">311589584</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-06</t>
+          <t xml:space="preserve">2032-03-31</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -11831,25 +11831,25 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t xml:space="preserve">2510279</t>
+          <t xml:space="preserve">5369956</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F237">
-        <v>296</v>
+        <v>1004</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t xml:space="preserve">311571120</t>
+          <t xml:space="preserve">311589590</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-07</t>
+          <t xml:space="preserve">2032-03-31</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -11881,25 +11881,25 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440066</t>
+          <t xml:space="preserve">9520978</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F238">
-        <v>1552</v>
+        <v>628</v>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t xml:space="preserve">311571176</t>
+          <t xml:space="preserve">311601922</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-07</t>
+          <t xml:space="preserve">2032-05-20</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -11931,25 +11931,25 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440066</t>
+          <t xml:space="preserve">9520978</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t xml:space="preserve">29</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F239">
-        <v>2501</v>
+        <v>629</v>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t xml:space="preserve">311571740</t>
+          <t xml:space="preserve">311604586</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-11</t>
+          <t xml:space="preserve">2032-06-01</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -11981,7 +11981,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t xml:space="preserve">1321129</t>
+          <t xml:space="preserve">720602, 5356897</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -11990,16 +11990,16 @@
         </is>
       </c>
       <c r="F240">
-        <v>260</v>
+        <v>450</v>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t xml:space="preserve">311571899</t>
+          <t xml:space="preserve">311632678</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-12</t>
+          <t xml:space="preserve">2032-10-03</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -12031,25 +12031,25 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t xml:space="preserve">1321129</t>
+          <t xml:space="preserve">5365512</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F241">
-        <v>256</v>
+        <v>912</v>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t xml:space="preserve">311571899</t>
+          <t xml:space="preserve">311661747</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-12</t>
+          <t xml:space="preserve">2033-02-22</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -12081,25 +12081,25 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t xml:space="preserve">1321129</t>
+          <t xml:space="preserve">100054057</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F242">
-        <v>285</v>
+        <v>728</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t xml:space="preserve">311571899</t>
+          <t xml:space="preserve">311680792</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-12</t>
+          <t xml:space="preserve">2033-05-15</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -12131,25 +12131,25 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t xml:space="preserve">2515317</t>
+          <t xml:space="preserve">100054057</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F243">
-        <v>290</v>
+        <v>1718</v>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t xml:space="preserve">311571952</t>
+          <t xml:space="preserve">311680792</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-12</t>
+          <t xml:space="preserve">2033-05-15</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -12181,25 +12181,25 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t xml:space="preserve">274699, 274700</t>
+          <t xml:space="preserve">100054057</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F244">
-        <v>2350</v>
+        <v>1718</v>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t xml:space="preserve">311571866</t>
+          <t xml:space="preserve">311680792</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-12</t>
+          <t xml:space="preserve">2033-05-15</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -12231,7 +12231,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t xml:space="preserve">5372195</t>
+          <t xml:space="preserve">100054057</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -12240,16 +12240,16 @@
         </is>
       </c>
       <c r="F245">
-        <v>2115</v>
+        <v>3496</v>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t xml:space="preserve">311572013</t>
+          <t xml:space="preserve">311680792</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-12</t>
+          <t xml:space="preserve">2033-05-15</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -12281,7 +12281,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t xml:space="preserve">5372195</t>
+          <t xml:space="preserve">100054057</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -12290,16 +12290,16 @@
         </is>
       </c>
       <c r="F246">
-        <v>1513</v>
+        <v>3496</v>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t xml:space="preserve">311572023</t>
+          <t xml:space="preserve">311680792</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-12</t>
+          <t xml:space="preserve">2033-05-15</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -12331,7 +12331,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t xml:space="preserve">2510166</t>
+          <t xml:space="preserve">9767630</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -12340,16 +12340,16 @@
         </is>
       </c>
       <c r="F247">
-        <v>3182</v>
+        <v>291</v>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t xml:space="preserve">311572673</t>
+          <t xml:space="preserve">311711092</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-17</t>
+          <t xml:space="preserve">2033-09-28</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -12381,25 +12381,25 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t xml:space="preserve">5372017</t>
+          <t xml:space="preserve">100592874, 100938157</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F248">
-        <v>2825</v>
+        <v>260</v>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t xml:space="preserve">311573634</t>
+          <t xml:space="preserve">311800388</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-20</t>
+          <t xml:space="preserve">2034-12-01</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -12431,7 +12431,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t xml:space="preserve">5356675</t>
+          <t xml:space="preserve">5367461</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -12440,16 +12440,16 @@
         </is>
       </c>
       <c r="F249">
-        <v>2434</v>
+        <v>7831</v>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t xml:space="preserve">311573780</t>
+          <t xml:space="preserve">311815213</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-21</t>
+          <t xml:space="preserve">2035-03-04</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -12481,25 +12481,25 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t xml:space="preserve">1321129</t>
+          <t xml:space="preserve">5367461</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F250">
-        <v>271</v>
+        <v>367</v>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t xml:space="preserve">311574234</t>
+          <t xml:space="preserve">311815213</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-24</t>
+          <t xml:space="preserve">2035-03-04</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -12531,25 +12531,25 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440066</t>
+          <t xml:space="preserve">5367461</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F251">
-        <v>4912</v>
+        <v>655</v>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t xml:space="preserve">311578788</t>
+          <t xml:space="preserve">311815213</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-15</t>
+          <t xml:space="preserve">2035-03-04</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -12581,25 +12581,25 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t xml:space="preserve">5369956</t>
+          <t xml:space="preserve">5367461</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F252">
-        <v>678</v>
+        <v>404</v>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t xml:space="preserve">311579598</t>
+          <t xml:space="preserve">311815213</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-18</t>
+          <t xml:space="preserve">2035-03-04</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -12631,25 +12631,25 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t xml:space="preserve">5369956</t>
+          <t xml:space="preserve">5365689</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F253">
-        <v>814</v>
+        <v>365</v>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t xml:space="preserve">311579613</t>
+          <t xml:space="preserve">311818322</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-18</t>
+          <t xml:space="preserve">2035-03-18</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t xml:space="preserve">5364595</t>
+          <t xml:space="preserve">5364995</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -12690,16 +12690,16 @@
         </is>
       </c>
       <c r="F254">
-        <v>790</v>
+        <v>422</v>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t xml:space="preserve">311584819</t>
+          <t xml:space="preserve">311821328</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-14</t>
+          <t xml:space="preserve">2035-03-31</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -12731,25 +12731,25 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t xml:space="preserve">5364595</t>
+          <t xml:space="preserve">8007086</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F255">
-        <v>1676</v>
+        <v>405</v>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t xml:space="preserve">311585992</t>
+          <t xml:space="preserve">311833542</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-17</t>
+          <t xml:space="preserve">2035-05-22</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -12781,25 +12781,25 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t xml:space="preserve">5369956</t>
+          <t xml:space="preserve">8268643</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F256">
-        <v>2450</v>
+        <v>449</v>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588963</t>
+          <t xml:space="preserve">311842884</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-29</t>
+          <t xml:space="preserve">2035-07-04</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -12831,7 +12831,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t xml:space="preserve">5369956</t>
+          <t xml:space="preserve">5374388</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -12840,16 +12840,16 @@
         </is>
       </c>
       <c r="F257">
-        <v>1827</v>
+        <v>1460</v>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t xml:space="preserve">311589574</t>
+          <t xml:space="preserve">311843932</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-31</t>
+          <t xml:space="preserve">2035-07-09</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -12881,25 +12881,25 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t xml:space="preserve">5369956</t>
+          <t xml:space="preserve">5369723</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F258">
-        <v>1031</v>
+        <v>1997</v>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t xml:space="preserve">311589584</t>
+          <t xml:space="preserve">311844993</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-31</t>
+          <t xml:space="preserve">2035-07-16</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -12931,25 +12931,25 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t xml:space="preserve">5369956</t>
+          <t xml:space="preserve">7010193</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F259">
-        <v>1004</v>
+        <v>4051</v>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t xml:space="preserve">311589590</t>
+          <t xml:space="preserve">311857461</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-31</t>
+          <t xml:space="preserve">2035-07-29</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -12981,25 +12981,25 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t xml:space="preserve">9520978</t>
+          <t xml:space="preserve">9449078</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F260">
-        <v>628</v>
+        <v>253</v>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t xml:space="preserve">311601922</t>
+          <t xml:space="preserve">311853833</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-20</t>
+          <t xml:space="preserve">2035-09-05</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -13031,7 +13031,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t xml:space="preserve">9520978</t>
+          <t xml:space="preserve">9449078</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -13040,16 +13040,16 @@
         </is>
       </c>
       <c r="F261">
-        <v>629</v>
+        <v>583</v>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t xml:space="preserve">311604586</t>
+          <t xml:space="preserve">311853851</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-01</t>
+          <t xml:space="preserve">2035-09-05</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -13081,25 +13081,25 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t xml:space="preserve">720602, 5356897</t>
+          <t xml:space="preserve">9449078</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F262">
-        <v>450</v>
+        <v>275</v>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t xml:space="preserve">311632678</t>
+          <t xml:space="preserve">311853849</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-10-03</t>
+          <t xml:space="preserve">2035-09-05</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -13131,25 +13131,25 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t xml:space="preserve">5365512</t>
+          <t xml:space="preserve">9449078</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F263">
-        <v>912</v>
+        <v>1520</v>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661747</t>
+          <t xml:space="preserve">311853850</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-22</t>
+          <t xml:space="preserve">2035-09-05</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -13181,25 +13181,25 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t xml:space="preserve">276565</t>
+          <t xml:space="preserve">5357819</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F264">
-        <v>683</v>
+        <v>1400</v>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t xml:space="preserve">311665571</t>
+          <t xml:space="preserve">311854216</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-10</t>
+          <t xml:space="preserve">2035-09-08</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -13231,25 +13231,25 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t xml:space="preserve">273337</t>
+          <t xml:space="preserve">5357820</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F265">
-        <v>1016</v>
+        <v>982</v>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669717</t>
+          <t xml:space="preserve">311854204</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-21</t>
+          <t xml:space="preserve">2035-09-08</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -13281,7 +13281,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t xml:space="preserve">9767630</t>
+          <t xml:space="preserve">10097609</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -13290,16 +13290,16 @@
         </is>
       </c>
       <c r="F266">
-        <v>291</v>
+        <v>393</v>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t xml:space="preserve">311711092</t>
+          <t xml:space="preserve">311856284</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-28</t>
+          <t xml:space="preserve">2035-09-17</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -13331,25 +13331,25 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t xml:space="preserve">100592874, 100938157</t>
+          <t xml:space="preserve">5353038</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F267">
-        <v>260</v>
+        <v>842</v>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t xml:space="preserve">311800388</t>
+          <t xml:space="preserve">311865606</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-12-01</t>
+          <t xml:space="preserve">2035-10-31</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -13381,25 +13381,25 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t xml:space="preserve">5367461</t>
+          <t xml:space="preserve">9375962</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F268">
-        <v>7831</v>
+        <v>871</v>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t xml:space="preserve">311815213</t>
+          <t xml:space="preserve">311865691</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-04</t>
+          <t xml:space="preserve">2035-10-31</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -13431,25 +13431,25 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t xml:space="preserve">5367461</t>
+          <t xml:space="preserve">9440066</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F269">
-        <v>367</v>
+        <v>882</v>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t xml:space="preserve">311815213</t>
+          <t xml:space="preserve">311865671</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-04</t>
+          <t xml:space="preserve">2035-10-31</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -13481,25 +13481,25 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t xml:space="preserve">5367461</t>
+          <t xml:space="preserve">9440066</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F270">
-        <v>655</v>
+        <v>805</v>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t xml:space="preserve">311815213</t>
+          <t xml:space="preserve">311865671</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-04</t>
+          <t xml:space="preserve">2035-10-31</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -13531,25 +13531,25 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t xml:space="preserve">5367461</t>
+          <t xml:space="preserve">9440066</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="F271">
-        <v>404</v>
+        <v>677</v>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t xml:space="preserve">311815213</t>
+          <t xml:space="preserve">311865671</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-04</t>
+          <t xml:space="preserve">2035-10-31</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -13581,25 +13581,25 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t xml:space="preserve">5365689</t>
+          <t xml:space="preserve">9440066</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F272">
-        <v>365</v>
+        <v>693</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t xml:space="preserve">311818322</t>
+          <t xml:space="preserve">311865671</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-18</t>
+          <t xml:space="preserve">2035-10-31</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -13631,25 +13631,25 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t xml:space="preserve">5364995</t>
+          <t xml:space="preserve">9440066</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="F273">
-        <v>422</v>
+        <v>693</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821328</t>
+          <t xml:space="preserve">311865671</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-31</t>
+          <t xml:space="preserve">2035-10-31</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -13686,20 +13686,20 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="F274">
-        <v>805</v>
+        <v>693</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t xml:space="preserve">311822471</t>
+          <t xml:space="preserve">311865671</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-03</t>
+          <t xml:space="preserve">2035-10-31</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -13731,25 +13731,25 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t xml:space="preserve">8268643</t>
+          <t xml:space="preserve">9440066</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="F275">
-        <v>449</v>
+        <v>693</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t xml:space="preserve">311842884</t>
+          <t xml:space="preserve">311865671</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-04</t>
+          <t xml:space="preserve">2035-10-31</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -13781,25 +13781,25 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t xml:space="preserve">5374388</t>
+          <t xml:space="preserve">9440066</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F276">
-        <v>1460</v>
+        <v>528</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t xml:space="preserve">311843932</t>
+          <t xml:space="preserve">311865671</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-09</t>
+          <t xml:space="preserve">2035-10-31</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -13831,25 +13831,25 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t xml:space="preserve">5369723</t>
+          <t xml:space="preserve">9440066</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="F277">
-        <v>1997</v>
+        <v>731</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t xml:space="preserve">311844993</t>
+          <t xml:space="preserve">311865671</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-16</t>
+          <t xml:space="preserve">2035-10-31</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -13881,25 +13881,25 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t xml:space="preserve">7010193</t>
+          <t xml:space="preserve">9440066</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="F278">
-        <v>4051</v>
+        <v>714</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t xml:space="preserve">311857461</t>
+          <t xml:space="preserve">311865671</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-29</t>
+          <t xml:space="preserve">2035-10-31</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -13931,25 +13931,25 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t xml:space="preserve">9449078</t>
+          <t xml:space="preserve">9440066</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F279">
-        <v>253</v>
+        <v>697</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t xml:space="preserve">311853833</t>
+          <t xml:space="preserve">311865671</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-05</t>
+          <t xml:space="preserve">2035-10-31</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -13981,25 +13981,25 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t xml:space="preserve">9449078</t>
+          <t xml:space="preserve">9440066</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F280">
-        <v>583</v>
+        <v>692</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t xml:space="preserve">311853851</t>
+          <t xml:space="preserve">311865671</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-05</t>
+          <t xml:space="preserve">2035-10-31</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -14031,25 +14031,25 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t xml:space="preserve">9449078</t>
+          <t xml:space="preserve">9440066</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="F281">
-        <v>275</v>
+        <v>4912</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t xml:space="preserve">311853849</t>
+          <t xml:space="preserve">311865671</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-05</t>
+          <t xml:space="preserve">2035-10-31</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -14081,25 +14081,25 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t xml:space="preserve">9449078</t>
+          <t xml:space="preserve">9440066</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">29</t>
         </is>
       </c>
       <c r="F282">
-        <v>1520</v>
+        <v>2501</v>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t xml:space="preserve">311853850</t>
+          <t xml:space="preserve">311865671</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-05</t>
+          <t xml:space="preserve">2035-10-31</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -14131,25 +14131,25 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t xml:space="preserve">5357819</t>
+          <t xml:space="preserve">9440066</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F283">
-        <v>1400</v>
+        <v>1552</v>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t xml:space="preserve">311854216</t>
+          <t xml:space="preserve">311865671</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-08</t>
+          <t xml:space="preserve">2035-10-31</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -14181,25 +14181,25 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t xml:space="preserve">5357820</t>
+          <t xml:space="preserve">9440066</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F284">
-        <v>982</v>
+        <v>648</v>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t xml:space="preserve">311854204</t>
+          <t xml:space="preserve">311865671</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-08</t>
+          <t xml:space="preserve">2035-10-31</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -14231,25 +14231,25 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t xml:space="preserve">10097609</t>
+          <t xml:space="preserve">9440066</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F285">
-        <v>393</v>
+        <v>296</v>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t xml:space="preserve">311856284</t>
+          <t xml:space="preserve">311865671</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-17</t>
+          <t xml:space="preserve">2035-10-31</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -14281,25 +14281,25 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t xml:space="preserve">5353038</t>
+          <t xml:space="preserve">9440066</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F286">
-        <v>842</v>
+        <v>280</v>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t xml:space="preserve">311865606</t>
+          <t xml:space="preserve">311866467</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-31</t>
+          <t xml:space="preserve">2035-11-05</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -14331,25 +14331,25 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t xml:space="preserve">9375962</t>
+          <t xml:space="preserve">9065073</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F287">
-        <v>871</v>
+        <v>364</v>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t xml:space="preserve">311865691</t>
+          <t xml:space="preserve">311866935</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-31</t>
+          <t xml:space="preserve">2035-11-07</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -14386,20 +14386,20 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F288">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866467</t>
+          <t xml:space="preserve">311866933</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-05</t>
+          <t xml:space="preserve">2035-11-07</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -14431,25 +14431,25 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t xml:space="preserve">9065073</t>
+          <t xml:space="preserve">9440066</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F289">
-        <v>364</v>
+        <v>643</v>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866935</t>
+          <t xml:space="preserve">311867719</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-07</t>
+          <t xml:space="preserve">2035-11-12</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -14481,25 +14481,25 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440066</t>
+          <t xml:space="preserve">2476133</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F290">
-        <v>278</v>
+        <v>515</v>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866933</t>
+          <t xml:space="preserve">311868284</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-07</t>
+          <t xml:space="preserve">2035-11-14</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -14531,7 +14531,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440066</t>
+          <t xml:space="preserve">720933, 10220761</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -14540,16 +14540,16 @@
         </is>
       </c>
       <c r="F291">
-        <v>643</v>
+        <v>325</v>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t xml:space="preserve">311867719</t>
+          <t xml:space="preserve">311870709</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-12</t>
+          <t xml:space="preserve">2035-11-28</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -14581,25 +14581,25 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t xml:space="preserve">2476133</t>
+          <t xml:space="preserve">5362593</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F292">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868309</t>
+          <t xml:space="preserve">311871351</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-14</t>
+          <t xml:space="preserve">2035-12-02</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -14844,7 +14844,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t xml:space="preserve">311876651</t>
+          <t xml:space="preserve">311876511</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -14894,7 +14894,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t xml:space="preserve">311876582</t>
+          <t xml:space="preserve">311876511</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">

--- a/public/exports/29188505.xlsx
+++ b/public/exports/29188505.xlsx
@@ -91,26 +91,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Caspar Brands Plads 8</t>
+          <t xml:space="preserve">Bildsøvej 74B</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100177093</t>
+          <t xml:space="preserve">721054, 2534110</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H2">
-        <v>415</v>
+        <v>1637</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -151,26 +151,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flakkebjerg Hovedgade 36</t>
+          <t xml:space="preserve">Birkemosevej 15</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100671511</t>
+          <t xml:space="preserve">9375962</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H3">
-        <v>507</v>
+        <v>520</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -211,26 +211,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenlunden 5</t>
+          <t xml:space="preserve">Caspar Brands Plads 8</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2534067</t>
+          <t xml:space="preserve">100177093</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H4">
-        <v>462</v>
+        <v>415</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -271,26 +271,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 2</t>
+          <t xml:space="preserve">Flakkebjerg Hovedgade 36</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">4241</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2539618</t>
+          <t xml:space="preserve">100671511</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H5">
-        <v>481</v>
+        <v>507</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -331,7 +331,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sdr.Stationsvej 6</t>
+          <t xml:space="preserve">Fælledvej 4B</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -341,16 +341,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">273337</t>
+          <t xml:space="preserve">721044, 5370905</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H6">
-        <v>1016</v>
+        <v>3477</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -391,26 +391,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådmandshaven 1</t>
+          <t xml:space="preserve">Gamlevej 6</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">4230</t>
+          <t xml:space="preserve">4244</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">274342</t>
+          <t xml:space="preserve">721004, 2509084</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H7">
-        <v>853</v>
+        <v>543</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -451,26 +451,26 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smedegade 32A</t>
+          <t xml:space="preserve">Gammelgade 25</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4230</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">274699, 274700</t>
+          <t xml:space="preserve">721002, 5363768</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H8">
-        <v>2350</v>
+        <v>254</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -511,26 +511,26 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønningen 3</t>
+          <t xml:space="preserve">Holtengårdsvej 21</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4230</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">276565</t>
+          <t xml:space="preserve">9599949</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H9">
-        <v>683</v>
+        <v>314</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -571,26 +571,26 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jens Baggesens Gade 10</t>
+          <t xml:space="preserve">Holtengårdsvej 23</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4230</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">5352869</t>
+          <t xml:space="preserve">9599949</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H10">
-        <v>662</v>
+        <v>1389</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -631,26 +631,26 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jens Baggesens Gade 12</t>
+          <t xml:space="preserve">Holtengårdsvej 23</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4230</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5352869</t>
+          <t xml:space="preserve">9599949</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H11">
-        <v>779</v>
+        <v>2939</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kjærsvej 70</t>
+          <t xml:space="preserve">Jens Baggesens Gade 10</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -701,16 +701,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">5356213</t>
+          <t xml:space="preserve">5352869</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H12">
-        <v>428</v>
+        <v>662</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nor Alleen 4</t>
+          <t xml:space="preserve">Jens Baggesens Gade 12</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -761,16 +761,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">5356675</t>
+          <t xml:space="preserve">5352869</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H13">
-        <v>480</v>
+        <v>779</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marievangsvej 53</t>
+          <t xml:space="preserve">Kirkerupvej 16A</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -821,16 +821,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">5374254</t>
+          <t xml:space="preserve">720398, 2516752</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H14">
-        <v>850</v>
+        <v>2148</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -871,26 +871,26 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stationsvej 53A</t>
+          <t xml:space="preserve">Kjærsvej 70</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">4261</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">720393, 2512194</t>
+          <t xml:space="preserve">5356213</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H15">
-        <v>3065</v>
+        <v>428</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkerupvej 16A</t>
+          <t xml:space="preserve">Kongelyset 39</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -941,16 +941,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">720398, 2516752</t>
+          <t xml:space="preserve">721032, 5370836</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H16">
-        <v>2148</v>
+        <v>684</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -991,17 +991,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllevangen 51</t>
+          <t xml:space="preserve">Kongelyset 41</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">720571, 5357751</t>
+          <t xml:space="preserve">721071, 5370837</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="H17">
-        <v>435</v>
+        <v>360</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1051,17 +1051,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sorøvej 78A</t>
+          <t xml:space="preserve">Lerbakken 8</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">4230</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">720982, 2509856</t>
+          <t xml:space="preserve">721100, 9527589</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="H18">
-        <v>390</v>
+        <v>1400</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1111,26 +1111,26 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sorøvej 90</t>
+          <t xml:space="preserve">Marievangsvej 104</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">4230</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">720989, 2509860</t>
+          <t xml:space="preserve">721055, 5374101</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H19">
-        <v>2656</v>
+        <v>702</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1171,26 +1171,26 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sorøvej 90</t>
+          <t xml:space="preserve">Marievangsvej 53</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">4230</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">720989, 2509860</t>
+          <t xml:space="preserve">5374254</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H20">
-        <v>284</v>
+        <v>850</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1231,26 +1231,26 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammelgade 25</t>
+          <t xml:space="preserve">Møllevangen 51</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">4230</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">721002, 5363768</t>
+          <t xml:space="preserve">720571, 5357751</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H21">
-        <v>254</v>
+        <v>435</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1291,26 +1291,26 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gamlevej 6</t>
+          <t xml:space="preserve">Nor Alleen 4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">4244</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">721004, 2509084</t>
+          <t xml:space="preserve">5356675</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H22">
-        <v>543</v>
+        <v>480</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1351,26 +1351,26 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sorøvej 94</t>
+          <t xml:space="preserve">Oksebrovej 13</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">4230</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">721007, 2509892</t>
+          <t xml:space="preserve">721059, 9472289</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H23">
-        <v>320</v>
+        <v>430</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1411,26 +1411,26 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sorøvej 88A</t>
+          <t xml:space="preserve">Parkvej 41</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">4230</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">721023, 8228900</t>
+          <t xml:space="preserve">721034, 5370887</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H24">
-        <v>1434</v>
+        <v>586</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongelyset 39</t>
+          <t xml:space="preserve">Rosenlunden 5</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">721032, 5370836</t>
+          <t xml:space="preserve">2534067</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="H25">
-        <v>684</v>
+        <v>462</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 41</t>
+          <t xml:space="preserve">Skjoldsvej 8</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1541,16 +1541,16 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">721034, 5370887</t>
+          <t xml:space="preserve">721035, 9364264</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H26">
-        <v>586</v>
+        <v>2031</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1606,11 +1606,11 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H27">
-        <v>2031</v>
+        <v>550</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1651,26 +1651,26 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skjoldsvej 8</t>
+          <t xml:space="preserve">Skolevej 2</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4241</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">721035, 9364264</t>
+          <t xml:space="preserve">2539618</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H28">
-        <v>550</v>
+        <v>481</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1711,26 +1711,26 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Teglværksvej 11</t>
+          <t xml:space="preserve">Sorøvej 78A</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4230</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">721040, 5370710</t>
+          <t xml:space="preserve">720982, 2509856</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H29">
-        <v>289</v>
+        <v>390</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1771,26 +1771,26 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fælledvej 4B</t>
+          <t xml:space="preserve">Sorøvej 88A</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4230</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">721044, 5370905</t>
+          <t xml:space="preserve">721023, 8228900</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H30">
-        <v>3477</v>
+        <v>1434</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1831,17 +1831,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bildsøvej 74B</t>
+          <t xml:space="preserve">Sorøvej 90</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4230</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">721054, 2534110</t>
+          <t xml:space="preserve">720989, 2509860</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="H31">
-        <v>1637</v>
+        <v>2656</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1891,26 +1891,26 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marievangsvej 104</t>
+          <t xml:space="preserve">Sorøvej 90</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4230</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">721055, 5374101</t>
+          <t xml:space="preserve">720989, 2509860</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H32">
-        <v>702</v>
+        <v>284</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1951,26 +1951,26 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oksebrovej 13</t>
+          <t xml:space="preserve">Sorøvej 94</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4230</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">721059, 9472289</t>
+          <t xml:space="preserve">721007, 2509892</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H33">
-        <v>430</v>
+        <v>320</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2011,17 +2011,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongelyset 41</t>
+          <t xml:space="preserve">Stationsvej 53A</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4261</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">721071, 5370837</t>
+          <t xml:space="preserve">720393, 2512194</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="H34">
-        <v>360</v>
+        <v>3065</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2071,26 +2071,26 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lerbakken 8</t>
+          <t xml:space="preserve">Teglværksvej 11</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">721100, 9527589</t>
+          <t xml:space="preserve">721040, 5370710</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H35">
-        <v>1400</v>
+        <v>289</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2131,40 +2131,40 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkemosevej 15</t>
+          <t xml:space="preserve">Rytterstaldstræde 8</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">9375962</t>
+          <t xml:space="preserve">5364758</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H36">
-        <v>520</v>
+        <v>382</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200044603</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2021-01-20</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2191,45 +2191,45 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holtengårdsvej 23</t>
+          <t xml:space="preserve">Oksebrovej 13</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">4230</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">9599949</t>
+          <t xml:space="preserve">721059, 9472289</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H37">
-        <v>1389</v>
+        <v>1269</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311269462</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2027-08-29</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -2251,17 +2251,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holtengårdsvej 23</t>
+          <t xml:space="preserve">Rosenkildevej 101B</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">4230</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">9599949</t>
+          <t xml:space="preserve">5369974</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2270,26 +2270,26 @@
         </is>
       </c>
       <c r="H38">
-        <v>2939</v>
+        <v>660</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311313206</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2028-05-09</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -2311,45 +2311,45 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holtengårdsvej 21</t>
+          <t xml:space="preserve">Rosenkildevej 101E</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">4230</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">9599949</t>
+          <t xml:space="preserve">5369974</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H39">
-        <v>314</v>
+        <v>604</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311313207</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2028-05-09</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rytterstaldstræde 8</t>
+          <t xml:space="preserve">Rosenkildevej 101H</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2381,35 +2381,35 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">5364758</t>
+          <t xml:space="preserve">5369974</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H40">
-        <v>382</v>
+        <v>604</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">200044603</t>
+          <t xml:space="preserve">311313201</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-01-20</t>
+          <t xml:space="preserve">2028-05-09</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oksebrovej 13</t>
+          <t xml:space="preserve">Skanderborgvej 9</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2441,25 +2441,25 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">721059, 9472289</t>
+          <t xml:space="preserve">9520978</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H41">
-        <v>1269</v>
+        <v>502</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311269462</t>
+          <t xml:space="preserve">311436999</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-29</t>
+          <t xml:space="preserve">2030-05-11</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2491,35 +2491,35 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenkildevej 101B</t>
+          <t xml:space="preserve">Birkemosevej 11</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">5369974</t>
+          <t xml:space="preserve">9375962</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H42">
-        <v>660</v>
+        <v>1707</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311313206</t>
+          <t xml:space="preserve">311446429</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-05-09</t>
+          <t xml:space="preserve">2030-06-28</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -2551,35 +2551,35 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenkildevej 101E</t>
+          <t xml:space="preserve">Birkemosevej 11</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">5369974</t>
+          <t xml:space="preserve">9375962</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H43">
-        <v>604</v>
+        <v>4059</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311313184</t>
+          <t xml:space="preserve">311446429</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-05-09</t>
+          <t xml:space="preserve">2030-06-28</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -2611,35 +2611,35 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenkildevej 101H</t>
+          <t xml:space="preserve">Birkemosevej 11</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">5369974</t>
+          <t xml:space="preserve">9375962</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H44">
-        <v>604</v>
+        <v>4347</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311313184</t>
+          <t xml:space="preserve">311446429</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-05-09</t>
+          <t xml:space="preserve">2030-06-28</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skanderborgvej 9</t>
+          <t xml:space="preserve">Anholtvej 5</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2681,25 +2681,25 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">9520978</t>
+          <t xml:space="preserve">5372046</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H45">
-        <v>502</v>
+        <v>1664</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311436999</t>
+          <t xml:space="preserve">311453409</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-05-11</t>
+          <t xml:space="preserve">2030-08-10</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -2731,17 +2731,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkemosevej 11</t>
+          <t xml:space="preserve">Bredegade 10</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">9375962</t>
+          <t xml:space="preserve">5364677</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2750,16 +2750,16 @@
         </is>
       </c>
       <c r="H46">
-        <v>1707</v>
+        <v>364</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311446429</t>
+          <t xml:space="preserve">311453373</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-06-28</t>
+          <t xml:space="preserve">2030-08-10</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkemosevej 11</t>
+          <t xml:space="preserve">Bernstensgade 3</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2801,25 +2801,25 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">9375962</t>
+          <t xml:space="preserve">5353467</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H47">
-        <v>4059</v>
+        <v>1060</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311446429</t>
+          <t xml:space="preserve">311455687</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-06-28</t>
+          <t xml:space="preserve">2030-08-20</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkemosevej 11</t>
+          <t xml:space="preserve">Bernstensgade 3</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2861,25 +2861,25 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">9375962</t>
+          <t xml:space="preserve">5353467</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H48">
-        <v>4347</v>
+        <v>749</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311446429</t>
+          <t xml:space="preserve">311455707</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-06-28</t>
+          <t xml:space="preserve">2030-08-20</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -2911,35 +2911,35 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredegade 10</t>
+          <t xml:space="preserve">Blomstervænget 3B</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4261</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">5364677</t>
+          <t xml:space="preserve">7000144</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H49">
-        <v>364</v>
+        <v>262</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311453373</t>
+          <t xml:space="preserve">311459626</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-08-10</t>
+          <t xml:space="preserve">2030-09-07</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -2971,17 +2971,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anholtvej 5</t>
+          <t xml:space="preserve">Blomstervænget 4</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4261</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">5372046</t>
+          <t xml:space="preserve">2512265</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2990,16 +2990,16 @@
         </is>
       </c>
       <c r="H50">
-        <v>1664</v>
+        <v>256</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311453409</t>
+          <t xml:space="preserve">311459672</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-08-10</t>
+          <t xml:space="preserve">2030-09-08</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3031,35 +3031,35 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernstensgade 3</t>
+          <t xml:space="preserve">Blomstervænget 5</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4261</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">5353467</t>
+          <t xml:space="preserve">7000144</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H51">
-        <v>1060</v>
+        <v>885</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311455687</t>
+          <t xml:space="preserve">311459816</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-08-20</t>
+          <t xml:space="preserve">2030-09-09</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3091,35 +3091,35 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernstensgade 3</t>
+          <t xml:space="preserve">Baldersvej 18</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">5353467</t>
+          <t xml:space="preserve">5369364</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H52">
-        <v>749</v>
+        <v>679</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311455707</t>
+          <t xml:space="preserve">311460826</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-08-20</t>
+          <t xml:space="preserve">2030-09-14</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blomstervænget 3B</t>
+          <t xml:space="preserve">Blomstervænget 5</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3166,20 +3166,20 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H53">
-        <v>262</v>
+        <v>1556</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311459626</t>
+          <t xml:space="preserve">311461439</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-07</t>
+          <t xml:space="preserve">2030-09-16</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blomstervænget 4</t>
+          <t xml:space="preserve">Blomstervænget 5</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3221,25 +3221,25 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2512265</t>
+          <t xml:space="preserve">7000144</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H54">
-        <v>256</v>
+        <v>1254</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311459672</t>
+          <t xml:space="preserve">311461378</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-08</t>
+          <t xml:space="preserve">2030-09-16</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3286,20 +3286,20 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H55">
-        <v>885</v>
+        <v>1859</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311459816</t>
+          <t xml:space="preserve">311462922</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-09</t>
+          <t xml:space="preserve">2030-09-23</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baldersvej 18</t>
+          <t xml:space="preserve">Bildsøvej 74C</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">5369364</t>
+          <t xml:space="preserve">2534110</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3350,16 +3350,16 @@
         </is>
       </c>
       <c r="H56">
-        <v>679</v>
+        <v>410</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311460826</t>
+          <t xml:space="preserve">311463733</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-14</t>
+          <t xml:space="preserve">2030-09-28</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3391,35 +3391,35 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blomstervænget 5</t>
+          <t xml:space="preserve">Bildsøvej 80B</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">4261</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">7000144</t>
+          <t xml:space="preserve">2534051</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H57">
-        <v>1556</v>
+        <v>930</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311461439</t>
+          <t xml:space="preserve">311463999</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-16</t>
+          <t xml:space="preserve">2030-09-29</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3451,35 +3451,35 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blomstervænget 5</t>
+          <t xml:space="preserve">Bildsøvej 80A</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">4261</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">7000144</t>
+          <t xml:space="preserve">2534051</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H58">
-        <v>1254</v>
+        <v>490</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311461378</t>
+          <t xml:space="preserve">311464413</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-16</t>
+          <t xml:space="preserve">2030-09-30</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3511,35 +3511,35 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blomstervænget 5</t>
+          <t xml:space="preserve">Jens Baggesens Gade 28</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">4261</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">7000144</t>
+          <t xml:space="preserve">5352875</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H59">
-        <v>1859</v>
+        <v>445</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311462922</t>
+          <t xml:space="preserve">311467112</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-23</t>
+          <t xml:space="preserve">2030-10-14</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bildsøvej 74C</t>
+          <t xml:space="preserve">Bildsøvej 80A</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2534110</t>
+          <t xml:space="preserve">2534051</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3590,16 +3590,16 @@
         </is>
       </c>
       <c r="H60">
-        <v>410</v>
+        <v>3133</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311463733</t>
+          <t xml:space="preserve">311467354</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-28</t>
+          <t xml:space="preserve">2030-10-15</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -3631,35 +3631,35 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bildsøvej 80B</t>
+          <t xml:space="preserve">Jens Baggesens Gade 28</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2534051</t>
+          <t xml:space="preserve">5352875</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H61">
-        <v>930</v>
+        <v>1023</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311463999</t>
+          <t xml:space="preserve">311467413</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-29</t>
+          <t xml:space="preserve">2030-10-15</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -3691,35 +3691,35 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bildsøvej 80A</t>
+          <t xml:space="preserve">Birchnersgade 1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2534051</t>
+          <t xml:space="preserve">5352875</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H62">
-        <v>490</v>
+        <v>5199</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311464413</t>
+          <t xml:space="preserve">311467646</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-30</t>
+          <t xml:space="preserve">2030-10-16</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jens Baggesens Gade 28</t>
+          <t xml:space="preserve">Birchnersgade 1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3766,20 +3766,20 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H63">
-        <v>445</v>
+        <v>323</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311467112</t>
+          <t xml:space="preserve">311467633</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-14</t>
+          <t xml:space="preserve">2030-10-16</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -3811,35 +3811,35 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bildsøvej 80A</t>
+          <t xml:space="preserve">Teilmanns Alle 6</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2534051</t>
+          <t xml:space="preserve">5352875</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H64">
-        <v>3133</v>
+        <v>1385</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311467354</t>
+          <t xml:space="preserve">311467558</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-15</t>
+          <t xml:space="preserve">2030-10-16</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -3871,17 +3871,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jens Baggesens Gade 28</t>
+          <t xml:space="preserve">Benediktevej 1</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">5352875</t>
+          <t xml:space="preserve">5374374</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3890,16 +3890,16 @@
         </is>
       </c>
       <c r="H65">
-        <v>1023</v>
+        <v>393</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311467413</t>
+          <t xml:space="preserve">311473973</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-15</t>
+          <t xml:space="preserve">2030-11-09</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -3931,35 +3931,35 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birchnersgade 1</t>
+          <t xml:space="preserve">Holmstrupvej 3</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">5352875</t>
+          <t xml:space="preserve">8268643</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H66">
-        <v>5199</v>
+        <v>790</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311467646</t>
+          <t xml:space="preserve">311480270</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-16</t>
+          <t xml:space="preserve">2030-12-03</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Teilmanns Alle 6</t>
+          <t xml:space="preserve">Skovvej 122B</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4001,25 +4001,25 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">5352875</t>
+          <t xml:space="preserve">10085726</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H67">
-        <v>1385</v>
+        <v>613</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311467558</t>
+          <t xml:space="preserve">311480291</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-16</t>
+          <t xml:space="preserve">2030-12-03</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4051,35 +4051,35 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birchnersgade 1</t>
+          <t xml:space="preserve">Borgbjergvej 18</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4242</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">5352875</t>
+          <t xml:space="preserve">9445550</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H68">
-        <v>323</v>
+        <v>1646</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311467633</t>
+          <t xml:space="preserve">311480862</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-16</t>
+          <t xml:space="preserve">2030-12-06</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Benediktevej 1</t>
+          <t xml:space="preserve">Willemoesvej 2C</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4121,25 +4121,25 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">5374374</t>
+          <t xml:space="preserve">9817467</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H69">
-        <v>393</v>
+        <v>636</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311473973</t>
+          <t xml:space="preserve">311484273</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-09</t>
+          <t xml:space="preserve">2030-12-21</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4171,17 +4171,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvej 122B</t>
+          <t xml:space="preserve">Rødtjørnevej 2</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">10085726</t>
+          <t xml:space="preserve">8872440</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4190,16 +4190,16 @@
         </is>
       </c>
       <c r="H70">
-        <v>613</v>
+        <v>1053</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311480291</t>
+          <t xml:space="preserve">311486475</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-03</t>
+          <t xml:space="preserve">2031-01-08</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holmstrupvej 3</t>
+          <t xml:space="preserve">Frederikshøjvej 3</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">8268643</t>
+          <t xml:space="preserve">5370888</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4250,16 +4250,16 @@
         </is>
       </c>
       <c r="H71">
-        <v>790</v>
+        <v>1207</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311480270</t>
+          <t xml:space="preserve">311487360</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-03</t>
+          <t xml:space="preserve">2031-01-13</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4291,17 +4291,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borgbjergvej 18</t>
+          <t xml:space="preserve">Kalundborgvej 59A</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">4242</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">9445550</t>
+          <t xml:space="preserve">7182253</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4310,16 +4310,16 @@
         </is>
       </c>
       <c r="H72">
-        <v>1646</v>
+        <v>3047</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311480862</t>
+          <t xml:space="preserve">311487437</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-06</t>
+          <t xml:space="preserve">2031-01-13</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Willemoesvej 2C</t>
+          <t xml:space="preserve">Rosenkildevej 59A</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4361,25 +4361,25 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">9817467</t>
+          <t xml:space="preserve">100008386</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H73">
-        <v>636</v>
+        <v>2040</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311484273</t>
+          <t xml:space="preserve">311487487</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-21</t>
+          <t xml:space="preserve">2031-01-13</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4411,17 +4411,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rødtjørnevej 2</t>
+          <t xml:space="preserve">Hovstien 36</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4242</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">8872440</t>
+          <t xml:space="preserve">2530706</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4430,16 +4430,16 @@
         </is>
       </c>
       <c r="H74">
-        <v>1053</v>
+        <v>407</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311486475</t>
+          <t xml:space="preserve">311487941</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-08</t>
+          <t xml:space="preserve">2031-01-15</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -4471,35 +4471,35 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenkildevej 59A</t>
+          <t xml:space="preserve">Gammelgade 10</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4230</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">100008386</t>
+          <t xml:space="preserve">5363727</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H75">
-        <v>2040</v>
+        <v>3534</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311487487</t>
+          <t xml:space="preserve">311490037</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-13</t>
+          <t xml:space="preserve">2031-01-25</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -4531,35 +4531,35 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederikshøjvej 3</t>
+          <t xml:space="preserve">Gammelgade 10</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4230</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">5370888</t>
+          <t xml:space="preserve">5363727</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H76">
-        <v>1207</v>
+        <v>364</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311487360</t>
+          <t xml:space="preserve">311490038</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-13</t>
+          <t xml:space="preserve">2031-01-25</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -4591,35 +4591,35 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalundborgvej 59A</t>
+          <t xml:space="preserve">Gammelgade 10</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4230</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">7182253</t>
+          <t xml:space="preserve">5363727</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H77">
-        <v>3047</v>
+        <v>3430</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311487437</t>
+          <t xml:space="preserve">311491016</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-13</t>
+          <t xml:space="preserve">2031-01-28</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -4651,35 +4651,35 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovstien 36</t>
+          <t xml:space="preserve">Gammelgade 10</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">4242</t>
+          <t xml:space="preserve">4230</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2530706</t>
+          <t xml:space="preserve">5363727</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H78">
-        <v>407</v>
+        <v>260</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311487941</t>
+          <t xml:space="preserve">311491019</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-15</t>
+          <t xml:space="preserve">2031-01-28</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -4711,35 +4711,35 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammelgade 10</t>
+          <t xml:space="preserve">Næstved Landevej 626</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">4230</t>
+          <t xml:space="preserve">4243</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">5363727</t>
+          <t xml:space="preserve">2517720</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H79">
-        <v>3534</v>
+        <v>263</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311490037</t>
+          <t xml:space="preserve">311491922</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-25</t>
+          <t xml:space="preserve">2031-02-01</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -4786,20 +4786,20 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H80">
-        <v>364</v>
+        <v>1072</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311490038</t>
+          <t xml:space="preserve">311492470</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-25</t>
+          <t xml:space="preserve">2031-02-03</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -4831,35 +4831,35 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammelgade 10</t>
+          <t xml:space="preserve">Næstved Landevej 632A</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">4230</t>
+          <t xml:space="preserve">4243</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">5363727</t>
+          <t xml:space="preserve">9316694</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H81">
-        <v>3430</v>
+        <v>2935</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311491016</t>
+          <t xml:space="preserve">311493661</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-28</t>
+          <t xml:space="preserve">2031-02-08</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -4891,35 +4891,35 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammelgade 10</t>
+          <t xml:space="preserve">Skolevej 2</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">4230</t>
+          <t xml:space="preserve">4241</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">5363727</t>
+          <t xml:space="preserve">2539618</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H82">
-        <v>260</v>
+        <v>2279</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311491019</t>
+          <t xml:space="preserve">311497388</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-28</t>
+          <t xml:space="preserve">2031-02-22</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -4951,17 +4951,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Næstved Landevej 626</t>
+          <t xml:space="preserve">Hvilebjergvej 6</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">4243</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2517720</t>
+          <t xml:space="preserve">2516751</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4970,16 +4970,16 @@
         </is>
       </c>
       <c r="H83">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311491922</t>
+          <t xml:space="preserve">311500800</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-01</t>
+          <t xml:space="preserve">2031-03-05</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5011,35 +5011,35 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammelgade 10</t>
+          <t xml:space="preserve">Kirkerupvej 18A</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">4230</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">5363727</t>
+          <t xml:space="preserve">2516403</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H84">
-        <v>1072</v>
+        <v>591</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311492470</t>
+          <t xml:space="preserve">311501345</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-03</t>
+          <t xml:space="preserve">2031-03-08</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5071,35 +5071,35 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Næstved Landevej 632A</t>
+          <t xml:space="preserve">Kirkerupvej 18A</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">4243</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">9316694</t>
+          <t xml:space="preserve">2516403</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H85">
-        <v>2935</v>
+        <v>590</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311493661</t>
+          <t xml:space="preserve">311501407</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-08</t>
+          <t xml:space="preserve">2031-03-08</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5146,20 +5146,20 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H86">
-        <v>2279</v>
+        <v>340</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311497388</t>
+          <t xml:space="preserve">311501290</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-22</t>
+          <t xml:space="preserve">2031-03-08</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5191,22 +5191,22 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvilebjergvej 6</t>
+          <t xml:space="preserve">Skolevej 2</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4241</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2516751</t>
+          <t xml:space="preserve">2539618</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H87">
@@ -5214,12 +5214,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311500800</t>
+          <t xml:space="preserve">311501280</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-05</t>
+          <t xml:space="preserve">2031-03-08</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5251,35 +5251,35 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkerupvej 18A</t>
+          <t xml:space="preserve">Næstved Landevej 624</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4243</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2516403</t>
+          <t xml:space="preserve">2513983</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H88">
-        <v>591</v>
+        <v>1688</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311501345</t>
+          <t xml:space="preserve">311504717</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-08</t>
+          <t xml:space="preserve">2031-03-18</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5311,35 +5311,35 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkerupvej 18A</t>
+          <t xml:space="preserve">Grevsensgade 6</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2516403</t>
+          <t xml:space="preserve">5352425</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H89">
-        <v>590</v>
+        <v>395</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311501407</t>
+          <t xml:space="preserve">311505192</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-08</t>
+          <t xml:space="preserve">2031-03-19</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5371,35 +5371,35 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 2</t>
+          <t xml:space="preserve">Jordbærvej 4</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">4241</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2539618</t>
+          <t xml:space="preserve">100072359</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H90">
-        <v>340</v>
+        <v>284</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311501290</t>
+          <t xml:space="preserve">311505101</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-08</t>
+          <t xml:space="preserve">2031-03-19</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5431,35 +5431,35 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 2</t>
+          <t xml:space="preserve">Storebæltsvej 5</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">4241</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2539618</t>
+          <t xml:space="preserve">7961746</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H91">
-        <v>277</v>
+        <v>722</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311501280</t>
+          <t xml:space="preserve">311504987</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-08</t>
+          <t xml:space="preserve">2031-03-19</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -5491,17 +5491,17 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Næstved Landevej 624</t>
+          <t xml:space="preserve">Vejsgårdparken 4</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">4243</t>
+          <t xml:space="preserve">4241</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2513983</t>
+          <t xml:space="preserve">9037913</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -5510,16 +5510,16 @@
         </is>
       </c>
       <c r="H92">
-        <v>1688</v>
+        <v>452</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311504717</t>
+          <t xml:space="preserve">311506197</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-18</t>
+          <t xml:space="preserve">2031-03-23</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -5551,17 +5551,17 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jordbærvej 4</t>
+          <t xml:space="preserve">Park Alle 4A</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4230</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">100072359</t>
+          <t xml:space="preserve">5362736</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -5570,16 +5570,16 @@
         </is>
       </c>
       <c r="H93">
-        <v>284</v>
+        <v>327</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311505101</t>
+          <t xml:space="preserve">311506439</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-19</t>
+          <t xml:space="preserve">2031-03-24</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -5611,17 +5611,17 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grevsensgade 6</t>
+          <t xml:space="preserve">Strandgade 14A</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4230</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">5352425</t>
+          <t xml:space="preserve">9316745</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -5630,16 +5630,16 @@
         </is>
       </c>
       <c r="H94">
-        <v>395</v>
+        <v>476</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311505192</t>
+          <t xml:space="preserve">311507001</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-19</t>
+          <t xml:space="preserve">2031-03-25</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -5671,17 +5671,17 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storebæltsvej 5</t>
+          <t xml:space="preserve">Vestergade 4</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4230</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">7961746</t>
+          <t xml:space="preserve">5362459</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -5690,16 +5690,16 @@
         </is>
       </c>
       <c r="H95">
-        <v>722</v>
+        <v>1312</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311504987</t>
+          <t xml:space="preserve">311506875</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-19</t>
+          <t xml:space="preserve">2031-03-25</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -5731,17 +5731,17 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vejsgårdparken 4</t>
+          <t xml:space="preserve">Skovvej 10A</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">4241</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">9037913</t>
+          <t xml:space="preserve">5355644</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -5750,16 +5750,16 @@
         </is>
       </c>
       <c r="H96">
-        <v>452</v>
+        <v>566</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311506197</t>
+          <t xml:space="preserve">311507425</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-23</t>
+          <t xml:space="preserve">2031-03-26</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -5791,17 +5791,17 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Park Alle 4A</t>
+          <t xml:space="preserve">Kastanievej 12A</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">4230</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">5362736</t>
+          <t xml:space="preserve">100069270</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -5810,16 +5810,16 @@
         </is>
       </c>
       <c r="H97">
-        <v>327</v>
+        <v>1327</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311506439</t>
+          <t xml:space="preserve">311508092</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-24</t>
+          <t xml:space="preserve">2031-03-29</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 4</t>
+          <t xml:space="preserve">Smidstrupvej 7</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">5362459</t>
+          <t xml:space="preserve">9508283</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -5870,16 +5870,16 @@
         </is>
       </c>
       <c r="H98">
-        <v>1312</v>
+        <v>1358</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311506875</t>
+          <t xml:space="preserve">311508161</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-25</t>
+          <t xml:space="preserve">2031-03-29</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandgade 14A</t>
+          <t xml:space="preserve">Stigsnæs Landevej 531</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">9316745</t>
+          <t xml:space="preserve">8525426</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -5930,16 +5930,16 @@
         </is>
       </c>
       <c r="H99">
-        <v>476</v>
+        <v>350</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311507001</t>
+          <t xml:space="preserve">311508001</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-25</t>
+          <t xml:space="preserve">2031-03-29</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -5971,17 +5971,17 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvej 10A</t>
+          <t xml:space="preserve">Skolevej 2</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4241</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">5355644</t>
+          <t xml:space="preserve">2539618</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -5990,16 +5990,16 @@
         </is>
       </c>
       <c r="H100">
-        <v>566</v>
+        <v>6548</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311507425</t>
+          <t xml:space="preserve">311508378</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-26</t>
+          <t xml:space="preserve">2031-03-30</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kastanievej 12A</t>
+          <t xml:space="preserve">Rådhuspladsen 11</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">100069270</t>
+          <t xml:space="preserve">5365177</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -6050,16 +6050,16 @@
         </is>
       </c>
       <c r="H101">
-        <v>1327</v>
+        <v>3715</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311508092</t>
+          <t xml:space="preserve">311519707</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-29</t>
+          <t xml:space="preserve">2031-05-12</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6091,17 +6091,17 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stigsnæs Landevej 531</t>
+          <t xml:space="preserve">Teilmanns Alle 12</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">4230</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">8525426</t>
+          <t xml:space="preserve">5352873</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -6110,16 +6110,16 @@
         </is>
       </c>
       <c r="H102">
-        <v>350</v>
+        <v>2690</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311508001</t>
+          <t xml:space="preserve">311520108</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-29</t>
+          <t xml:space="preserve">2031-05-14</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6151,17 +6151,17 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smidstrupvej 7</t>
+          <t xml:space="preserve">Stenstuegade 14</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">4230</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">9508283</t>
+          <t xml:space="preserve">5365401</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -6170,16 +6170,16 @@
         </is>
       </c>
       <c r="H103">
-        <v>1358</v>
+        <v>2835</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311508161</t>
+          <t xml:space="preserve">311520408</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-29</t>
+          <t xml:space="preserve">2031-05-17</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6211,17 +6211,17 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 2</t>
+          <t xml:space="preserve">Stenstuegade 3</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">4241</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2539618</t>
+          <t xml:space="preserve">5364701</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -6230,16 +6230,16 @@
         </is>
       </c>
       <c r="H104">
-        <v>6548</v>
+        <v>2349</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311508378</t>
+          <t xml:space="preserve">311520407</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-30</t>
+          <t xml:space="preserve">2031-05-17</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -6271,17 +6271,17 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhuspladsen 11</t>
+          <t xml:space="preserve">Vemmeløsevej 40</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4261</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">5365177</t>
+          <t xml:space="preserve">2512196</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -6290,16 +6290,16 @@
         </is>
       </c>
       <c r="H105">
-        <v>3715</v>
+        <v>2103</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311519707</t>
+          <t xml:space="preserve">311522349</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-12</t>
+          <t xml:space="preserve">2031-05-25</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Teilmanns Alle 12</t>
+          <t xml:space="preserve">Teglværksvej 4</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6341,25 +6341,25 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">5352873</t>
+          <t xml:space="preserve">2537303</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H106">
-        <v>2690</v>
+        <v>4083</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311520108</t>
+          <t xml:space="preserve">311522700</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-14</t>
+          <t xml:space="preserve">2031-05-26</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -6391,35 +6391,35 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenstuegade 3</t>
+          <t xml:space="preserve">Teglværksvej 4</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">5364701</t>
+          <t xml:space="preserve">2537303</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H107">
-        <v>2349</v>
+        <v>750</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311520407</t>
+          <t xml:space="preserve">311523579</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-17</t>
+          <t xml:space="preserve">2031-05-28</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenstuegade 14</t>
+          <t xml:space="preserve">Sdr.Stationsvej 26</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">5365401</t>
+          <t xml:space="preserve">5365703</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -6470,16 +6470,16 @@
         </is>
       </c>
       <c r="H108">
-        <v>2835</v>
+        <v>2240</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311520408</t>
+          <t xml:space="preserve">311525535</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-17</t>
+          <t xml:space="preserve">2031-06-04</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -6511,35 +6511,35 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vemmeløsevej 40</t>
+          <t xml:space="preserve">Rosenkildevej 92</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">4261</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2512196</t>
+          <t xml:space="preserve">5367460</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H109">
-        <v>2103</v>
+        <v>588</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311522349</t>
+          <t xml:space="preserve">311525861</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-25</t>
+          <t xml:space="preserve">2031-06-07</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -6571,35 +6571,35 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Teglværksvej 4</t>
+          <t xml:space="preserve">Willemoesvej 2B</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2537303</t>
+          <t xml:space="preserve">9817467</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H110">
-        <v>4083</v>
+        <v>3634</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311522700</t>
+          <t xml:space="preserve">311527772</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-26</t>
+          <t xml:space="preserve">2031-06-14</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -6631,35 +6631,35 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Teglværksvej 4</t>
+          <t xml:space="preserve">Willemoesvej 2D</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2537303</t>
+          <t xml:space="preserve">9817467</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H111">
-        <v>750</v>
+        <v>1430</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311523579</t>
+          <t xml:space="preserve">311527791</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-28</t>
+          <t xml:space="preserve">2031-06-14</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sdr.Stationsvej 26</t>
+          <t xml:space="preserve">Kastanievej 12</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -6701,7 +6701,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">5365703</t>
+          <t xml:space="preserve">5366424</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -6710,16 +6710,16 @@
         </is>
       </c>
       <c r="H112">
-        <v>2240</v>
+        <v>890</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311525535</t>
+          <t xml:space="preserve">311528110</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-04</t>
+          <t xml:space="preserve">2031-06-15</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -6751,35 +6751,35 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenkildevej 92</t>
+          <t xml:space="preserve">Heilmannsvej 31A</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4230</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">5367460</t>
+          <t xml:space="preserve">2510445</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H113">
-        <v>588</v>
+        <v>350</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311525853</t>
+          <t xml:space="preserve">311529584</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-07</t>
+          <t xml:space="preserve">2031-06-21</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -6811,17 +6811,17 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Willemoesvej 2B</t>
+          <t xml:space="preserve">Kildebakken 7</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">9817467</t>
+          <t xml:space="preserve">2538510</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -6830,16 +6830,16 @@
         </is>
       </c>
       <c r="H114">
-        <v>3634</v>
+        <v>534</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311527772</t>
+          <t xml:space="preserve">311529569</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-14</t>
+          <t xml:space="preserve">2031-06-21</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Willemoesvej 2D</t>
+          <t xml:space="preserve">Nørrevangstorvet 8</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -6881,25 +6881,25 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">9817467</t>
+          <t xml:space="preserve">5367674</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H115">
-        <v>1430</v>
+        <v>2009</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311527791</t>
+          <t xml:space="preserve">311530847</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-14</t>
+          <t xml:space="preserve">2031-06-24</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -6931,17 +6931,17 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kastanievej 12</t>
+          <t xml:space="preserve">Hesselbyvej 29</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4230</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">5366424</t>
+          <t xml:space="preserve">100044819</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -6950,16 +6950,16 @@
         </is>
       </c>
       <c r="H116">
-        <v>890</v>
+        <v>588</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311528110</t>
+          <t xml:space="preserve">311531573</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-15</t>
+          <t xml:space="preserve">2031-06-28</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -6991,17 +6991,17 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heilmannsvej 31A</t>
+          <t xml:space="preserve">Industrivej 9</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">4230</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2510445</t>
+          <t xml:space="preserve">5369721</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -7010,16 +7010,16 @@
         </is>
       </c>
       <c r="H117">
-        <v>350</v>
+        <v>1154</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311529584</t>
+          <t xml:space="preserve">311531549</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-21</t>
+          <t xml:space="preserve">2031-06-28</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildebakken 7</t>
+          <t xml:space="preserve">Lilleskovvej 3</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7061,7 +7061,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2538510</t>
+          <t xml:space="preserve">5356211</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -7070,16 +7070,16 @@
         </is>
       </c>
       <c r="H118">
-        <v>534</v>
+        <v>717</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311529569</t>
+          <t xml:space="preserve">311531545</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-21</t>
+          <t xml:space="preserve">2031-06-28</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -7111,17 +7111,17 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrevangstorvet 8</t>
+          <t xml:space="preserve">Kastaniealleen 1</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4230</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">5367674</t>
+          <t xml:space="preserve">2510023</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -7130,16 +7130,16 @@
         </is>
       </c>
       <c r="H119">
-        <v>2009</v>
+        <v>755</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311530847</t>
+          <t xml:space="preserve">311532382</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-24</t>
+          <t xml:space="preserve">2031-06-30</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -7171,17 +7171,17 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hesselbyvej 29</t>
+          <t xml:space="preserve">Nygårdsvej 2</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">4230</t>
+          <t xml:space="preserve">4241</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">100044819</t>
+          <t xml:space="preserve">100037421</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -7190,16 +7190,16 @@
         </is>
       </c>
       <c r="H120">
-        <v>588</v>
+        <v>382</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311531573</t>
+          <t xml:space="preserve">311532441</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-28</t>
+          <t xml:space="preserve">2031-06-30</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -7231,35 +7231,35 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lilleskovvej 3</t>
+          <t xml:space="preserve">Nygårdsvej 2</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4241</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">5356211</t>
+          <t xml:space="preserve">100037421</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H121">
-        <v>717</v>
+        <v>301</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311531545</t>
+          <t xml:space="preserve">311532439</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-28</t>
+          <t xml:space="preserve">2031-06-30</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Industrivej 9</t>
+          <t xml:space="preserve">Oehlenschlægersgade 7</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">5369721</t>
+          <t xml:space="preserve">5366539</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -7310,16 +7310,16 @@
         </is>
       </c>
       <c r="H122">
-        <v>1154</v>
+        <v>957</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311531554</t>
+          <t xml:space="preserve">311532388</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-28</t>
+          <t xml:space="preserve">2031-06-30</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -7351,17 +7351,17 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygårdsvej 2</t>
+          <t xml:space="preserve">Halsebyvænget 1</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve">4241</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">100037421</t>
+          <t xml:space="preserve">2538114</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -7370,16 +7370,16 @@
         </is>
       </c>
       <c r="H123">
-        <v>382</v>
+        <v>270</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311532441</t>
+          <t xml:space="preserve">311532763</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-30</t>
+          <t xml:space="preserve">2031-07-01</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -7411,17 +7411,17 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygårdsvej 2</t>
+          <t xml:space="preserve">Halsebyvænget 3</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">4241</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">100037421</t>
+          <t xml:space="preserve">2538114</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -7430,16 +7430,16 @@
         </is>
       </c>
       <c r="H124">
-        <v>301</v>
+        <v>367</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311532439</t>
+          <t xml:space="preserve">311532763</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-30</t>
+          <t xml:space="preserve">2031-07-01</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -7471,35 +7471,35 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kastaniealleen 1</t>
+          <t xml:space="preserve">Østre Alle 67</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve">4230</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2510023</t>
+          <t xml:space="preserve">5366711</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H125">
-        <v>755</v>
+        <v>307</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311532382</t>
+          <t xml:space="preserve">311539234</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-30</t>
+          <t xml:space="preserve">2031-08-05</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oehlenschlægersgade 7</t>
+          <t xml:space="preserve">Østre Alle 67</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -7541,25 +7541,25 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">5366539</t>
+          <t xml:space="preserve">5366711</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H126">
-        <v>957</v>
+        <v>1748</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311532388</t>
+          <t xml:space="preserve">311539376</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-30</t>
+          <t xml:space="preserve">2031-08-06</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -7591,35 +7591,35 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halsebyvænget 1</t>
+          <t xml:space="preserve">Østre Alle 67</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2538114</t>
+          <t xml:space="preserve">5366711</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="H127">
-        <v>270</v>
+        <v>1479</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311532763</t>
+          <t xml:space="preserve">311539398</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-01</t>
+          <t xml:space="preserve">2031-08-06</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -7651,35 +7651,35 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halsebyvænget 3</t>
+          <t xml:space="preserve">Kirkerupvej 18B</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2538114</t>
+          <t xml:space="preserve">2516403</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H128">
-        <v>367</v>
+        <v>3007</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311532763</t>
+          <t xml:space="preserve">311539671</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-01</t>
+          <t xml:space="preserve">2031-08-09</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -7726,20 +7726,20 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H129">
-        <v>307</v>
+        <v>3351</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539234</t>
+          <t xml:space="preserve">311539622</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-05</t>
+          <t xml:space="preserve">2031-08-09</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -7786,20 +7786,20 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H130">
-        <v>1748</v>
+        <v>2511</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539376</t>
+          <t xml:space="preserve">311539622</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-06</t>
+          <t xml:space="preserve">2031-08-09</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -7846,20 +7846,20 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H131">
-        <v>1479</v>
+        <v>1140</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539398</t>
+          <t xml:space="preserve">311539622</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-06</t>
+          <t xml:space="preserve">2031-08-09</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkerupvej 18B</t>
+          <t xml:space="preserve">Sejerøvej 1</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -7901,7 +7901,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2516403</t>
+          <t xml:space="preserve">5372045</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -7910,16 +7910,16 @@
         </is>
       </c>
       <c r="H132">
-        <v>3007</v>
+        <v>1205</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539671</t>
+          <t xml:space="preserve">311539841</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-09</t>
+          <t xml:space="preserve">2031-08-10</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Alle 67</t>
+          <t xml:space="preserve">Sejerøvej 1</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -7961,25 +7961,25 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">5366711</t>
+          <t xml:space="preserve">5372045</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H133">
-        <v>3351</v>
+        <v>1120</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539622</t>
+          <t xml:space="preserve">311540151</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-09</t>
+          <t xml:space="preserve">2031-08-11</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -8011,7 +8011,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Alle 67</t>
+          <t xml:space="preserve">Langes Gård 2</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8021,25 +8021,25 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">5366711</t>
+          <t xml:space="preserve">5365298</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H134">
-        <v>2511</v>
+        <v>1409</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539622</t>
+          <t xml:space="preserve">311540403</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-09</t>
+          <t xml:space="preserve">2031-08-12</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -8071,35 +8071,35 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Alle 67</t>
+          <t xml:space="preserve">Gamlevej 2</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4244</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">5366711</t>
+          <t xml:space="preserve">2509084</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H135">
-        <v>1140</v>
+        <v>338</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539622</t>
+          <t xml:space="preserve">311541914</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-09</t>
+          <t xml:space="preserve">2031-08-19</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -8146,20 +8146,20 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H136">
-        <v>1205</v>
+        <v>4812</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539841</t>
+          <t xml:space="preserve">311542201</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-10</t>
+          <t xml:space="preserve">2031-08-20</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -8206,20 +8206,20 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H137">
-        <v>1120</v>
+        <v>1061</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311540151</t>
+          <t xml:space="preserve">311542780</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-11</t>
+          <t xml:space="preserve">2031-08-24</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -8251,7 +8251,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langes Gård 2</t>
+          <t xml:space="preserve">Sejerøvej 1</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -8261,25 +8261,25 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">5365298</t>
+          <t xml:space="preserve">5372045</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H138">
-        <v>1409</v>
+        <v>4921</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311540403</t>
+          <t xml:space="preserve">311543723</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-12</t>
+          <t xml:space="preserve">2031-08-27</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -8311,35 +8311,35 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gamlevej 2</t>
+          <t xml:space="preserve">Sejerøvej 1</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t xml:space="preserve">4244</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509084</t>
+          <t xml:space="preserve">5372045</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H139">
-        <v>338</v>
+        <v>531</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311541914</t>
+          <t xml:space="preserve">311544102</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-19</t>
+          <t xml:space="preserve">2031-08-30</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -8386,20 +8386,20 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H140">
-        <v>4812</v>
+        <v>550</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311542201</t>
+          <t xml:space="preserve">311544121</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-20</t>
+          <t xml:space="preserve">2031-08-30</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -8446,20 +8446,20 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H141">
-        <v>1061</v>
+        <v>2205</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311542780</t>
+          <t xml:space="preserve">311544116</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-24</t>
+          <t xml:space="preserve">2031-08-30</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -8491,35 +8491,35 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sejerøvej 1</t>
+          <t xml:space="preserve">Rådmandshaven 1</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4230</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">5372045</t>
+          <t xml:space="preserve">274342</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H142">
-        <v>4921</v>
+        <v>853</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311543723</t>
+          <t xml:space="preserve">311544492</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-27</t>
+          <t xml:space="preserve">2031-08-31</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -8551,35 +8551,35 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sejerøvej 1</t>
+          <t xml:space="preserve">Teglværksparken 50</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">5372045</t>
+          <t xml:space="preserve">5354432</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H143">
-        <v>531</v>
+        <v>1732</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311544102</t>
+          <t xml:space="preserve">311544586</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-30</t>
+          <t xml:space="preserve">2031-08-31</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -8611,7 +8611,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sejerøvej 1</t>
+          <t xml:space="preserve">Valmuevej 27</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -8621,25 +8621,25 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">5372045</t>
+          <t xml:space="preserve">100039122</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H144">
-        <v>550</v>
+        <v>1603</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311544121</t>
+          <t xml:space="preserve">311546941</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-30</t>
+          <t xml:space="preserve">2031-09-09</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -8671,35 +8671,35 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sejerøvej 1</t>
+          <t xml:space="preserve">Skolevej 8</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4230</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">5372045</t>
+          <t xml:space="preserve">2509761</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H145">
-        <v>2205</v>
+        <v>347</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311544116</t>
+          <t xml:space="preserve">311547265</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-30</t>
+          <t xml:space="preserve">2031-09-10</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -8731,35 +8731,35 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Teglværksparken 50</t>
+          <t xml:space="preserve">Skolevej 8</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4230</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">5354432</t>
+          <t xml:space="preserve">2509761</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="H146">
-        <v>1732</v>
+        <v>1684</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311544586</t>
+          <t xml:space="preserve">311547259</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-31</t>
+          <t xml:space="preserve">2031-09-10</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -8791,35 +8791,35 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valmuevej 27</t>
+          <t xml:space="preserve">Skolevej 8</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4230</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">100039122</t>
+          <t xml:space="preserve">2509761</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="H147">
-        <v>1603</v>
+        <v>412</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311546941</t>
+          <t xml:space="preserve">311547259</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-09</t>
+          <t xml:space="preserve">2031-09-10</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -8866,11 +8866,11 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="H148">
-        <v>347</v>
+        <v>672</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
@@ -8926,11 +8926,11 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="H149">
-        <v>1684</v>
+        <v>1564</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
@@ -8986,11 +8986,11 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H150">
-        <v>412</v>
+        <v>251</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
@@ -9031,30 +9031,30 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 8</t>
+          <t xml:space="preserve">Torvegade 15</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t xml:space="preserve">4230</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509761</t>
+          <t xml:space="preserve">5367350</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H151">
-        <v>672</v>
+        <v>2616</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547259</t>
+          <t xml:space="preserve">311547289</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -9091,30 +9091,30 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 8</t>
+          <t xml:space="preserve">Torvegade 22</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t xml:space="preserve">4230</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509761</t>
+          <t xml:space="preserve">5365179</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H152">
-        <v>1564</v>
+        <v>1527</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547259</t>
+          <t xml:space="preserve">311547442</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -9151,35 +9151,35 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 8</t>
+          <t xml:space="preserve">Dahlsvej 3</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t xml:space="preserve">4230</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509761</t>
+          <t xml:space="preserve">5352869</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H153">
-        <v>251</v>
+        <v>3202</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547259</t>
+          <t xml:space="preserve">311547605</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-10</t>
+          <t xml:space="preserve">2031-09-13</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -9211,17 +9211,17 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torvegade 22</t>
+          <t xml:space="preserve">Skolevej 8</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4230</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">5365179</t>
+          <t xml:space="preserve">2509761</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -9230,16 +9230,16 @@
         </is>
       </c>
       <c r="H154">
-        <v>1527</v>
+        <v>4519</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547442</t>
+          <t xml:space="preserve">311547586</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-10</t>
+          <t xml:space="preserve">2031-09-13</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -9271,35 +9271,35 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torvegade 15</t>
+          <t xml:space="preserve">Sorøvej 74</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4230</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">5367350</t>
+          <t xml:space="preserve">2509890</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H155">
-        <v>2616</v>
+        <v>622</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547289</t>
+          <t xml:space="preserve">311547660</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-10</t>
+          <t xml:space="preserve">2031-09-13</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -9331,7 +9331,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 8</t>
+          <t xml:space="preserve">Sorøvej 74</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -9341,20 +9341,20 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509761</t>
+          <t xml:space="preserve">2509890</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H156">
-        <v>4519</v>
+        <v>461</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547586</t>
+          <t xml:space="preserve">311547618</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -9391,7 +9391,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sorøvej 74</t>
+          <t xml:space="preserve">Møllebakken 3A</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -9401,25 +9401,25 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509890</t>
+          <t xml:space="preserve">5363800</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H157">
-        <v>622</v>
+        <v>364</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547660</t>
+          <t xml:space="preserve">311547982</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-13</t>
+          <t xml:space="preserve">2031-09-14</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -9451,35 +9451,35 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sorøvej 74</t>
+          <t xml:space="preserve">Gørtlergade 4</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t xml:space="preserve">4230</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509890</t>
+          <t xml:space="preserve">5371082</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H158">
-        <v>461</v>
+        <v>1244</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547618</t>
+          <t xml:space="preserve">311548237</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-13</t>
+          <t xml:space="preserve">2031-09-15</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -9511,35 +9511,35 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dahlsvej 3</t>
+          <t xml:space="preserve">Gormsvej 20</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">5352869</t>
+          <t xml:space="preserve">5373175</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H159">
-        <v>3202</v>
+        <v>874</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547605</t>
+          <t xml:space="preserve">311548621</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-13</t>
+          <t xml:space="preserve">2031-09-16</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -9571,17 +9571,17 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllebakken 3A</t>
+          <t xml:space="preserve">Caspar Brands Plads 6</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t xml:space="preserve">4230</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">5363800</t>
+          <t xml:space="preserve">5353043</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -9590,16 +9590,16 @@
         </is>
       </c>
       <c r="H160">
-        <v>364</v>
+        <v>1638</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547982</t>
+          <t xml:space="preserve">311549963</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-14</t>
+          <t xml:space="preserve">2031-09-22</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -9631,35 +9631,35 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gørtlergade 4</t>
+          <t xml:space="preserve">Borgergade 31F</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4241</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">5371082</t>
+          <t xml:space="preserve">2539906</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H161">
-        <v>1244</v>
+        <v>293</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311548237</t>
+          <t xml:space="preserve">311550259</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-15</t>
+          <t xml:space="preserve">2031-09-23</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -9691,35 +9691,35 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gormsvej 20</t>
+          <t xml:space="preserve">Borgbjergvej 5</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4242</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">5373175</t>
+          <t xml:space="preserve">2529964</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H162">
-        <v>874</v>
+        <v>691</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311548621</t>
+          <t xml:space="preserve">311550899</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-16</t>
+          <t xml:space="preserve">2031-09-27</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -9751,35 +9751,35 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Caspar Brands Plads 6</t>
+          <t xml:space="preserve">Borgbjergvej 5</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4242</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">5353043</t>
+          <t xml:space="preserve">2529964</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H163">
-        <v>1638</v>
+        <v>582</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549963</t>
+          <t xml:space="preserve">311550940</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-22</t>
+          <t xml:space="preserve">2031-09-27</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -9811,35 +9811,35 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borgergade 31F</t>
+          <t xml:space="preserve">Borgbjergvej 5</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t xml:space="preserve">4241</t>
+          <t xml:space="preserve">4242</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2539906</t>
+          <t xml:space="preserve">2529964</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H164">
-        <v>293</v>
+        <v>665</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311550259</t>
+          <t xml:space="preserve">311550949</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-23</t>
+          <t xml:space="preserve">2031-09-27</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -9871,17 +9871,17 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borgbjergvej 5</t>
+          <t xml:space="preserve">Borgergade 31A</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t xml:space="preserve">4242</t>
+          <t xml:space="preserve">4241</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2529964</t>
+          <t xml:space="preserve">2539906</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -9890,11 +9890,11 @@
         </is>
       </c>
       <c r="H165">
-        <v>691</v>
+        <v>262</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311550899</t>
+          <t xml:space="preserve">311551144</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -9931,17 +9931,17 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borgbjergvej 5</t>
+          <t xml:space="preserve">Borgergade 31B</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t xml:space="preserve">4242</t>
+          <t xml:space="preserve">4241</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2529964</t>
+          <t xml:space="preserve">2539906</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -9950,11 +9950,11 @@
         </is>
       </c>
       <c r="H166">
-        <v>582</v>
+        <v>262</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311550940</t>
+          <t xml:space="preserve">311551144</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -9991,17 +9991,17 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borgbjergvej 5</t>
+          <t xml:space="preserve">Borgergade 31C</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t xml:space="preserve">4242</t>
+          <t xml:space="preserve">4241</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2529964</t>
+          <t xml:space="preserve">2539906</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -10010,11 +10010,11 @@
         </is>
       </c>
       <c r="H167">
-        <v>665</v>
+        <v>302</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311550949</t>
+          <t xml:space="preserve">311551144</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -10051,7 +10051,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borgergade 31A</t>
+          <t xml:space="preserve">Borgergade 31D</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -10066,11 +10066,11 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H168">
-        <v>262</v>
+        <v>302</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borgergade 31B</t>
+          <t xml:space="preserve">Borgergade 31E</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H169">
@@ -10171,30 +10171,30 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borgergade 31C</t>
+          <t xml:space="preserve">Møllebjergvej 12</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t xml:space="preserve">4241</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2539906</t>
+          <t xml:space="preserve">9848819</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H170">
-        <v>302</v>
+        <v>1668</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311551144</t>
+          <t xml:space="preserve">311551003</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -10231,35 +10231,35 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borgergade 31D</t>
+          <t xml:space="preserve">Linde Alle 56</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t xml:space="preserve">4241</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2539906</t>
+          <t xml:space="preserve">5355580</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H171">
-        <v>302</v>
+        <v>564</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311551144</t>
+          <t xml:space="preserve">311551302</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-27</t>
+          <t xml:space="preserve">2031-09-28</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -10291,35 +10291,35 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borgergade 31E</t>
+          <t xml:space="preserve">Linde Alle 56</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t xml:space="preserve">4241</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2539906</t>
+          <t xml:space="preserve">5355580</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H172">
-        <v>262</v>
+        <v>280</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311551144</t>
+          <t xml:space="preserve">311551303</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-27</t>
+          <t xml:space="preserve">2031-09-28</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -10351,35 +10351,35 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllebjergvej 12</t>
+          <t xml:space="preserve">Holtengårdsvej 23</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4230</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">9848819</t>
+          <t xml:space="preserve">9599949</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H173">
-        <v>1668</v>
+        <v>660</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311551003</t>
+          <t xml:space="preserve">311552088</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-27</t>
+          <t xml:space="preserve">2031-09-30</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Linde Alle 56</t>
+          <t xml:space="preserve">Lützensvej 1</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -10421,25 +10421,25 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">5355580</t>
+          <t xml:space="preserve">9223561</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H174">
-        <v>564</v>
+        <v>1762</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311551302</t>
+          <t xml:space="preserve">311554266</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-28</t>
+          <t xml:space="preserve">2031-10-11</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -10471,7 +10471,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Linde Alle 56</t>
+          <t xml:space="preserve">Lützensvej 2</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -10481,25 +10481,25 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">5355580</t>
+          <t xml:space="preserve">9223561</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H175">
-        <v>280</v>
+        <v>1458</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311551303</t>
+          <t xml:space="preserve">311554279</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-28</t>
+          <t xml:space="preserve">2031-10-11</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -10531,35 +10531,35 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holtengårdsvej 23</t>
+          <t xml:space="preserve">Skolegade 1</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t xml:space="preserve">4230</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">9599949</t>
+          <t xml:space="preserve">5353438</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H176">
-        <v>660</v>
+        <v>4163</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311552088</t>
+          <t xml:space="preserve">311556144</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-30</t>
+          <t xml:space="preserve">2031-10-19</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -10591,7 +10591,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lützensvej 1</t>
+          <t xml:space="preserve">Skolegade 1</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -10601,25 +10601,25 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">9223561</t>
+          <t xml:space="preserve">5353438</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H177">
-        <v>1762</v>
+        <v>1262</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311554266</t>
+          <t xml:space="preserve">311556454</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-11</t>
+          <t xml:space="preserve">2031-10-20</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -10651,7 +10651,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lützensvej 2</t>
+          <t xml:space="preserve">Skolegade 1</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -10661,25 +10661,25 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">9223561</t>
+          <t xml:space="preserve">5353438</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H178">
-        <v>1458</v>
+        <v>2360</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311554279</t>
+          <t xml:space="preserve">311558566</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-11</t>
+          <t xml:space="preserve">2031-10-29</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -10711,17 +10711,17 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 1</t>
+          <t xml:space="preserve">Dalsvinget 13</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">5353438</t>
+          <t xml:space="preserve">5367089</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -10730,16 +10730,16 @@
         </is>
       </c>
       <c r="H179">
-        <v>4163</v>
+        <v>1770</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311556144</t>
+          <t xml:space="preserve">311558846</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-19</t>
+          <t xml:space="preserve">2031-11-01</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -10771,35 +10771,35 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 1</t>
+          <t xml:space="preserve">Dalsvinget 13</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">5353438</t>
+          <t xml:space="preserve">5367089</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H180">
-        <v>1262</v>
+        <v>561</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311556454</t>
+          <t xml:space="preserve">311558830</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-20</t>
+          <t xml:space="preserve">2031-11-01</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -10831,35 +10831,35 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 1</t>
+          <t xml:space="preserve">Ingemannsvej 24</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">5353438</t>
+          <t xml:space="preserve">10041598</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H181">
-        <v>2360</v>
+        <v>294</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558566</t>
+          <t xml:space="preserve">311558916</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-29</t>
+          <t xml:space="preserve">2031-11-01</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -10891,7 +10891,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ingemannsvej 24</t>
+          <t xml:space="preserve">Skovsøgade 10</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -10901,20 +10901,20 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">10041598</t>
+          <t xml:space="preserve">5364982</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H182">
-        <v>294</v>
+        <v>1101</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558916</t>
+          <t xml:space="preserve">311558955</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -10966,15 +10966,15 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H183">
-        <v>1101</v>
+        <v>1512</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558955</t>
+          <t xml:space="preserve">311558978</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -11011,35 +11011,35 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovsøgade 10</t>
+          <t xml:space="preserve">Quistgaardsvej 4</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t xml:space="preserve">5364982</t>
+          <t xml:space="preserve">5355259</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H184">
-        <v>1512</v>
+        <v>3102</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558978</t>
+          <t xml:space="preserve">311559245</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-01</t>
+          <t xml:space="preserve">2031-11-02</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dalsvinget 13</t>
+          <t xml:space="preserve">Skovsøgade 10</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -11081,25 +11081,25 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t xml:space="preserve">5367089</t>
+          <t xml:space="preserve">5364982</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H185">
-        <v>1770</v>
+        <v>1246</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558842</t>
+          <t xml:space="preserve">311559093</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-01</t>
+          <t xml:space="preserve">2031-11-02</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -11131,7 +11131,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dalsvinget 13</t>
+          <t xml:space="preserve">Ingemannsvej 26</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -11141,25 +11141,25 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">5367089</t>
+          <t xml:space="preserve">10041598</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H186">
-        <v>561</v>
+        <v>1218</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558842</t>
+          <t xml:space="preserve">311559440</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-01</t>
+          <t xml:space="preserve">2031-11-03</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -11191,17 +11191,17 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quistgaardsvej 4</t>
+          <t xml:space="preserve">Pilagervej 31</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">5355259</t>
+          <t xml:space="preserve">8063257</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -11210,16 +11210,16 @@
         </is>
       </c>
       <c r="H187">
-        <v>3102</v>
+        <v>1167</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311559245</t>
+          <t xml:space="preserve">311559529</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-02</t>
+          <t xml:space="preserve">2031-11-03</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -11251,35 +11251,35 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovsøgade 10</t>
+          <t xml:space="preserve">Halsebyvænget 28</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">5364982</t>
+          <t xml:space="preserve">100051113</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H188">
-        <v>1246</v>
+        <v>902</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311559093</t>
+          <t xml:space="preserve">311560225</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-02</t>
+          <t xml:space="preserve">2031-11-08</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
@@ -11311,7 +11311,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ingemannsvej 26</t>
+          <t xml:space="preserve">Fejøvej 1A</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -11321,7 +11321,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t xml:space="preserve">10041598</t>
+          <t xml:space="preserve">5372069</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -11330,16 +11330,16 @@
         </is>
       </c>
       <c r="H189">
-        <v>1218</v>
+        <v>735</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311559440</t>
+          <t xml:space="preserve">311561231</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-03</t>
+          <t xml:space="preserve">2031-11-11</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -11371,7 +11371,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pilagervej 31</t>
+          <t xml:space="preserve">Fejøvej 1A</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -11381,25 +11381,25 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">8063257</t>
+          <t xml:space="preserve">5372069</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H190">
-        <v>1167</v>
+        <v>266</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311559529</t>
+          <t xml:space="preserve">311561278</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-03</t>
+          <t xml:space="preserve">2031-11-11</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
@@ -11431,35 +11431,35 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halsebyvænget 28</t>
+          <t xml:space="preserve">Park Alle 48</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4230</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">100051113</t>
+          <t xml:space="preserve">100048065</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H191">
-        <v>902</v>
+        <v>754</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560289</t>
+          <t xml:space="preserve">311562131</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-08</t>
+          <t xml:space="preserve">2031-11-16</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
@@ -11491,35 +11491,35 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fejøvej 1A</t>
+          <t xml:space="preserve">Park Alle 70</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4230</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t xml:space="preserve">5372069</t>
+          <t xml:space="preserve">100048065</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H192">
-        <v>735</v>
+        <v>754</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311561231</t>
+          <t xml:space="preserve">311562138</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-11</t>
+          <t xml:space="preserve">2031-11-16</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -11551,35 +11551,35 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fejøvej 1A</t>
+          <t xml:space="preserve">Storebælts Erhvervspark 1</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">5372069</t>
+          <t xml:space="preserve">5353802</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H193">
-        <v>266</v>
+        <v>1229</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311561278</t>
+          <t xml:space="preserve">311564825</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-11</t>
+          <t xml:space="preserve">2031-11-29</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -11611,35 +11611,35 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Park Alle 48</t>
+          <t xml:space="preserve">Storebælts Erhvervspark 1</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t xml:space="preserve">4230</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t xml:space="preserve">100048065</t>
+          <t xml:space="preserve">5353802</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H194">
-        <v>754</v>
+        <v>1839</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562133</t>
+          <t xml:space="preserve">311564831</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-16</t>
+          <t xml:space="preserve">2031-11-29</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -11671,17 +11671,17 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Park Alle 70</t>
+          <t xml:space="preserve">Storebælts Erhvervspark 1</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t xml:space="preserve">4230</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">100048065</t>
+          <t xml:space="preserve">5353802</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -11690,16 +11690,16 @@
         </is>
       </c>
       <c r="H195">
-        <v>754</v>
+        <v>686</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562133</t>
+          <t xml:space="preserve">311564875</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-16</t>
+          <t xml:space="preserve">2031-11-29</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -11746,15 +11746,15 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H196">
-        <v>1229</v>
+        <v>590</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311564825</t>
+          <t xml:space="preserve">311564886</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -11791,35 +11791,35 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storebælts Erhvervspark 1</t>
+          <t xml:space="preserve">Næstvedvej 15</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4230</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">5353802</t>
+          <t xml:space="preserve">5362905</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H197">
-        <v>1839</v>
+        <v>3290</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311564831</t>
+          <t xml:space="preserve">311565082</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-29</t>
+          <t xml:space="preserve">2031-11-30</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -11851,7 +11851,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storebælts Erhvervspark 1</t>
+          <t xml:space="preserve">Nygade 45</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -11861,25 +11861,25 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t xml:space="preserve">5353802</t>
+          <t xml:space="preserve">5352531</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H198">
-        <v>686</v>
+        <v>1914</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311564875</t>
+          <t xml:space="preserve">311566478</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-29</t>
+          <t xml:space="preserve">2031-12-07</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -11911,35 +11911,35 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storebælts Erhvervspark 1</t>
+          <t xml:space="preserve">Sct.Pedersgade 18</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t xml:space="preserve">5353802</t>
+          <t xml:space="preserve">5367901</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H199">
-        <v>590</v>
+        <v>3906</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311564886</t>
+          <t xml:space="preserve">311566457</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-29</t>
+          <t xml:space="preserve">2031-12-07</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -11971,35 +11971,35 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Næstvedvej 15</t>
+          <t xml:space="preserve">Sct.Pedersgade 18</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t xml:space="preserve">4230</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t xml:space="preserve">5362905</t>
+          <t xml:space="preserve">5367901</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H200">
-        <v>3290</v>
+        <v>1443</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311565082</t>
+          <t xml:space="preserve">311566459</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-30</t>
+          <t xml:space="preserve">2031-12-07</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -12031,7 +12031,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 45</t>
+          <t xml:space="preserve">Slagelse Landevej 17</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t xml:space="preserve">5352531</t>
+          <t xml:space="preserve">7900308</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -12050,16 +12050,16 @@
         </is>
       </c>
       <c r="H201">
-        <v>1914</v>
+        <v>455</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311566473</t>
+          <t xml:space="preserve">311567544</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-07</t>
+          <t xml:space="preserve">2031-12-13</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -12091,7 +12091,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sct.Pedersgade 18</t>
+          <t xml:space="preserve">Holmstrupvej 5</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -12101,25 +12101,25 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t xml:space="preserve">5367901</t>
+          <t xml:space="preserve">5372195</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H202">
-        <v>3906</v>
+        <v>432</v>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311566457</t>
+          <t xml:space="preserve">311569003</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-07</t>
+          <t xml:space="preserve">2031-12-20</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -12151,7 +12151,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sct.Pedersgade 18</t>
+          <t xml:space="preserve">Holmstrupvej 5</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -12161,25 +12161,25 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t xml:space="preserve">5367901</t>
+          <t xml:space="preserve">5372195</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H203">
-        <v>1443</v>
+        <v>425</v>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311566459</t>
+          <t xml:space="preserve">311568977</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-07</t>
+          <t xml:space="preserve">2031-12-20</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -12211,35 +12211,35 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slagelse Landevej 17</t>
+          <t xml:space="preserve">Skjoldsvej 10</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t xml:space="preserve">7900308</t>
+          <t xml:space="preserve">5372195</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H204">
-        <v>455</v>
+        <v>680</v>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311567544</t>
+          <t xml:space="preserve">311568956</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-13</t>
+          <t xml:space="preserve">2031-12-20</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
@@ -12286,20 +12286,20 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H205">
-        <v>432</v>
+        <v>2423</v>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t xml:space="preserve">311569066</t>
+          <t xml:space="preserve">311569315</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-20</t>
+          <t xml:space="preserve">2031-12-21</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
@@ -12331,7 +12331,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skjoldsvej 10</t>
+          <t xml:space="preserve">Holmstrupvej 5</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -12346,20 +12346,20 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H206">
-        <v>680</v>
+        <v>655</v>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311569066</t>
+          <t xml:space="preserve">311569344</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-20</t>
+          <t xml:space="preserve">2031-12-21</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
@@ -12391,7 +12391,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holmstrupvej 5</t>
+          <t xml:space="preserve">Brovej 1</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -12401,25 +12401,25 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t xml:space="preserve">5372195</t>
+          <t xml:space="preserve">2532379</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H207">
-        <v>425</v>
+        <v>856</v>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311569066</t>
+          <t xml:space="preserve">311569765</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-20</t>
+          <t xml:space="preserve">2031-12-23</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
@@ -12451,7 +12451,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holmstrupvej 5</t>
+          <t xml:space="preserve">Brovej 1</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -12461,25 +12461,25 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t xml:space="preserve">5372195</t>
+          <t xml:space="preserve">2532379</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H208">
-        <v>2423</v>
+        <v>574</v>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311569315</t>
+          <t xml:space="preserve">311569773</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-21</t>
+          <t xml:space="preserve">2031-12-23</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
@@ -12511,7 +12511,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holmstrupvej 5</t>
+          <t xml:space="preserve">Holbækvej 16</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -12521,25 +12521,25 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t xml:space="preserve">5372195</t>
+          <t xml:space="preserve">5369490</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H209">
-        <v>655</v>
+        <v>553</v>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311569344</t>
+          <t xml:space="preserve">311569796</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-21</t>
+          <t xml:space="preserve">2031-12-23</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
@@ -12571,7 +12571,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brovej 1</t>
+          <t xml:space="preserve">Holbækvej 16</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -12581,20 +12581,20 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2532379</t>
+          <t xml:space="preserve">5369490</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H210">
-        <v>856</v>
+        <v>367</v>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311569779</t>
+          <t xml:space="preserve">311569852</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
@@ -12631,7 +12631,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brovej 1</t>
+          <t xml:space="preserve">Fælledvej 4</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -12641,25 +12641,25 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2532379</t>
+          <t xml:space="preserve">9364227</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H211">
-        <v>574</v>
+        <v>1738</v>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311569779</t>
+          <t xml:space="preserve">311570292</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-23</t>
+          <t xml:space="preserve">2032-01-03</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holbækvej 16</t>
+          <t xml:space="preserve">Hashøjvej 7</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -12701,7 +12701,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t xml:space="preserve">5369490</t>
+          <t xml:space="preserve">2532420</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -12710,16 +12710,16 @@
         </is>
       </c>
       <c r="H212">
-        <v>553</v>
+        <v>5003</v>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311569796</t>
+          <t xml:space="preserve">311570736</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-23</t>
+          <t xml:space="preserve">2032-01-05</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
@@ -12751,35 +12751,35 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holbækvej 16</t>
+          <t xml:space="preserve">Norvænget 22</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4230</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t xml:space="preserve">5369490</t>
+          <t xml:space="preserve">2510279</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H213">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311569852</t>
+          <t xml:space="preserve">311571124</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-23</t>
+          <t xml:space="preserve">2032-01-07</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
@@ -12811,35 +12811,35 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fælledvej 4</t>
+          <t xml:space="preserve">Norvænget 4</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4230</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t xml:space="preserve">9364227</t>
+          <t xml:space="preserve">2510279</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H214">
-        <v>1738</v>
+        <v>296</v>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311570292</t>
+          <t xml:space="preserve">311571120</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-03</t>
+          <t xml:space="preserve">2032-01-07</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
@@ -12871,7 +12871,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hashøjvej 7</t>
+          <t xml:space="preserve">Holmstrupvej 5</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -12881,25 +12881,25 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t xml:space="preserve">2532420</t>
+          <t xml:space="preserve">5372195</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H215">
-        <v>5003</v>
+        <v>2115</v>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311570736</t>
+          <t xml:space="preserve">311572013</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-05</t>
+          <t xml:space="preserve">2032-01-12</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
@@ -12931,35 +12931,35 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norvænget 22</t>
+          <t xml:space="preserve">Holmstrupvej 5</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t xml:space="preserve">4230</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t xml:space="preserve">2510279</t>
+          <t xml:space="preserve">5372195</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H216">
-        <v>369</v>
+        <v>1513</v>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t xml:space="preserve">311571124</t>
+          <t xml:space="preserve">311572023</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-07</t>
+          <t xml:space="preserve">2032-01-12</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
@@ -12991,35 +12991,35 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norvænget 4</t>
+          <t xml:space="preserve">Husmandsstræde 4A</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t xml:space="preserve">4230</t>
+          <t xml:space="preserve">4245</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t xml:space="preserve">2510279</t>
+          <t xml:space="preserve">2515317</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H217">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311571124</t>
+          <t xml:space="preserve">311571952</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-07</t>
+          <t xml:space="preserve">2032-01-12</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Husmandsstræde 4A</t>
+          <t xml:space="preserve">Smedegade 32A</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t xml:space="preserve">4245</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t xml:space="preserve">2515317</t>
+          <t xml:space="preserve">274699, 274700</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -13070,11 +13070,11 @@
         </is>
       </c>
       <c r="H218">
-        <v>290</v>
+        <v>2350</v>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311571952</t>
+          <t xml:space="preserve">311571866</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
@@ -13111,35 +13111,35 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holmstrupvej 5</t>
+          <t xml:space="preserve">Norvænget 5</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4230</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t xml:space="preserve">5372195</t>
+          <t xml:space="preserve">2510166</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H219">
-        <v>2115</v>
+        <v>3182</v>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t xml:space="preserve">311572013</t>
+          <t xml:space="preserve">311572673</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-12</t>
+          <t xml:space="preserve">2032-01-17</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
@@ -13171,7 +13171,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holmstrupvej 5</t>
+          <t xml:space="preserve">Antvorskov Alle 133</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -13181,25 +13181,25 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t xml:space="preserve">5372195</t>
+          <t xml:space="preserve">5372017</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H220">
-        <v>1513</v>
+        <v>2825</v>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t xml:space="preserve">311572023</t>
+          <t xml:space="preserve">311573634</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-12</t>
+          <t xml:space="preserve">2032-01-20</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
@@ -13231,17 +13231,17 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norvænget 5</t>
+          <t xml:space="preserve">Drøsselbjergvej 40A</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t xml:space="preserve">4230</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t xml:space="preserve">2510166</t>
+          <t xml:space="preserve">1321129</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -13250,16 +13250,16 @@
         </is>
       </c>
       <c r="H221">
-        <v>3182</v>
+        <v>260</v>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t xml:space="preserve">311572673</t>
+          <t xml:space="preserve">311573835</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-17</t>
+          <t xml:space="preserve">2032-01-21</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
@@ -13291,7 +13291,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Antvorskov Alle 133</t>
+          <t xml:space="preserve">Drøsselbjergvej 40A</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -13301,25 +13301,25 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t xml:space="preserve">5372017</t>
+          <t xml:space="preserve">1321129</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H222">
-        <v>2825</v>
+        <v>256</v>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t xml:space="preserve">311573634</t>
+          <t xml:space="preserve">311573835</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-20</t>
+          <t xml:space="preserve">2032-01-21</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
@@ -13366,11 +13366,11 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H223">
-        <v>260</v>
+        <v>285</v>
       </c>
       <c r="I223" t="inlineStr">
         <is>
@@ -13411,30 +13411,30 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drøsselbjergvej 40A</t>
+          <t xml:space="preserve">Nor Alleen 1</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t xml:space="preserve">1321129</t>
+          <t xml:space="preserve">5356675</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H224">
-        <v>256</v>
+        <v>2434</v>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t xml:space="preserve">311573835</t>
+          <t xml:space="preserve">311573780</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -13471,7 +13471,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drøsselbjergvej 40A</t>
+          <t xml:space="preserve">Drøsselbjergvej 42A</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -13486,20 +13486,20 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H225">
-        <v>285</v>
+        <v>271</v>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t xml:space="preserve">311573835</t>
+          <t xml:space="preserve">311574234</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-21</t>
+          <t xml:space="preserve">2032-01-24</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
@@ -13531,7 +13531,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nor Alleen 1</t>
+          <t xml:space="preserve">Tjærebyvej 17</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -13541,25 +13541,25 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t xml:space="preserve">5356675</t>
+          <t xml:space="preserve">2538110</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H226">
-        <v>2434</v>
+        <v>1834</v>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t xml:space="preserve">311573780</t>
+          <t xml:space="preserve">311577742</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-21</t>
+          <t xml:space="preserve">2032-02-09</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drøsselbjergvej 42A</t>
+          <t xml:space="preserve">Byskov Alle 41</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -13601,25 +13601,25 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t xml:space="preserve">1321129</t>
+          <t xml:space="preserve">5369956</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H227">
-        <v>271</v>
+        <v>678</v>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t xml:space="preserve">311574234</t>
+          <t xml:space="preserve">311579598</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-24</t>
+          <t xml:space="preserve">2032-02-18</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
@@ -13651,35 +13651,35 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjærebyvej 17</t>
+          <t xml:space="preserve">Byskov Alle 41</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t xml:space="preserve">2538110</t>
+          <t xml:space="preserve">5369956</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H228">
-        <v>1834</v>
+        <v>2077</v>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t xml:space="preserve">311577742</t>
+          <t xml:space="preserve">311579646</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-09</t>
+          <t xml:space="preserve">2032-02-18</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
@@ -13726,15 +13726,15 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H229">
-        <v>678</v>
+        <v>814</v>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t xml:space="preserve">311579598</t>
+          <t xml:space="preserve">311579613</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -13771,7 +13771,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byskov Alle 41</t>
+          <t xml:space="preserve">Bredegade 11A</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -13781,25 +13781,25 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t xml:space="preserve">5369956</t>
+          <t xml:space="preserve">5364595</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H230">
-        <v>2077</v>
+        <v>790</v>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t xml:space="preserve">311579646</t>
+          <t xml:space="preserve">311584819</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-18</t>
+          <t xml:space="preserve">2032-03-14</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
@@ -13831,7 +13831,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byskov Alle 41</t>
+          <t xml:space="preserve">Bredegade 11B</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -13841,25 +13841,25 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t xml:space="preserve">5369956</t>
+          <t xml:space="preserve">5364595</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H231">
-        <v>814</v>
+        <v>1676</v>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t xml:space="preserve">311579613</t>
+          <t xml:space="preserve">311585992</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-18</t>
+          <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
@@ -13891,7 +13891,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredegade 11A</t>
+          <t xml:space="preserve">Byskov Alle 41</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -13901,25 +13901,25 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t xml:space="preserve">5364595</t>
+          <t xml:space="preserve">5369956</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H232">
-        <v>790</v>
+        <v>2450</v>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311584819</t>
+          <t xml:space="preserve">311588963</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-14</t>
+          <t xml:space="preserve">2032-03-29</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredegade 11B</t>
+          <t xml:space="preserve">Byskov Alle 41</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -13961,25 +13961,25 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t xml:space="preserve">5364595</t>
+          <t xml:space="preserve">5369956</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H233">
-        <v>1676</v>
+        <v>1827</v>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t xml:space="preserve">311585992</t>
+          <t xml:space="preserve">311589574</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-17</t>
+          <t xml:space="preserve">2032-03-31</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
@@ -14026,20 +14026,20 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H234">
-        <v>2450</v>
+        <v>1031</v>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588963</t>
+          <t xml:space="preserve">311589584</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-29</t>
+          <t xml:space="preserve">2032-03-31</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
@@ -14086,15 +14086,15 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H235">
-        <v>1827</v>
+        <v>1004</v>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t xml:space="preserve">311589574</t>
+          <t xml:space="preserve">311589590</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -14131,7 +14131,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byskov Alle 41</t>
+          <t xml:space="preserve">Skanderborgvej 9</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -14141,25 +14141,25 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t xml:space="preserve">5369956</t>
+          <t xml:space="preserve">9520978</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H236">
-        <v>1031</v>
+        <v>628</v>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t xml:space="preserve">311589584</t>
+          <t xml:space="preserve">311601922</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-31</t>
+          <t xml:space="preserve">2032-05-20</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
@@ -14191,7 +14191,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byskov Alle 41</t>
+          <t xml:space="preserve">Skanderborgvej 9</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -14201,25 +14201,25 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t xml:space="preserve">5369956</t>
+          <t xml:space="preserve">9520978</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H237">
-        <v>1004</v>
+        <v>629</v>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t xml:space="preserve">311589590</t>
+          <t xml:space="preserve">311604586</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-31</t>
+          <t xml:space="preserve">2032-06-01</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
@@ -14251,35 +14251,35 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skanderborgvej 9</t>
+          <t xml:space="preserve">Korsør Lystskov 20</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t xml:space="preserve">9520978</t>
+          <t xml:space="preserve">720602, 5356897</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H238">
-        <v>628</v>
+        <v>450</v>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t xml:space="preserve">311601922</t>
+          <t xml:space="preserve">311632678</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-20</t>
+          <t xml:space="preserve">2032-10-03</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
@@ -14311,7 +14311,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skanderborgvej 9</t>
+          <t xml:space="preserve">Svendsgade 104</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -14321,25 +14321,25 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t xml:space="preserve">9520978</t>
+          <t xml:space="preserve">5365512</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H239">
-        <v>629</v>
+        <v>912</v>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t xml:space="preserve">311604586</t>
+          <t xml:space="preserve">311661747</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-01</t>
+          <t xml:space="preserve">2033-02-22</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
@@ -14371,35 +14371,35 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Korsør Lystskov 20</t>
+          <t xml:space="preserve">Grønningen 3</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t xml:space="preserve">720602, 5356897</t>
+          <t xml:space="preserve">276565</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H240">
-        <v>450</v>
+        <v>683</v>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t xml:space="preserve">311632678</t>
+          <t xml:space="preserve">311665571</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-10-03</t>
+          <t xml:space="preserve">2033-03-10</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
@@ -14431,7 +14431,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svendsgade 104</t>
+          <t xml:space="preserve">Sdr.Stationsvej 6</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -14441,7 +14441,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t xml:space="preserve">5365512</t>
+          <t xml:space="preserve">273337</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
@@ -14450,16 +14450,16 @@
         </is>
       </c>
       <c r="H241">
-        <v>912</v>
+        <v>1016</v>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661747</t>
+          <t xml:space="preserve">311669717</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-22</t>
+          <t xml:space="preserve">2033-03-21</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
@@ -14911,7 +14911,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrevangstorvet 6D</t>
+          <t xml:space="preserve">Nørrevangstorvet 6A</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -14926,11 +14926,11 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H249">
-        <v>7831</v>
+        <v>655</v>
       </c>
       <c r="I249" t="inlineStr">
         <is>
@@ -15031,7 +15031,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrevangstorvet 6A</t>
+          <t xml:space="preserve">Nørrevangstorvet 6D</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -15046,11 +15046,11 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H251">
-        <v>655</v>
+        <v>7831</v>
       </c>
       <c r="I251" t="inlineStr">
         <is>
@@ -15991,7 +15991,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søbatteriet 17</t>
+          <t xml:space="preserve">Bragesvej 6</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -16001,20 +16001,20 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t xml:space="preserve">5353038</t>
+          <t xml:space="preserve">9375962</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H267">
-        <v>842</v>
+        <v>871</v>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t xml:space="preserve">311865606</t>
+          <t xml:space="preserve">311865691</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
@@ -16051,30 +16051,30 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bragesvej 6</t>
+          <t xml:space="preserve">Rosenkildevej 47</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t xml:space="preserve">9375962</t>
+          <t xml:space="preserve">9440066</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H268">
-        <v>871</v>
+        <v>882</v>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t xml:space="preserve">311865691</t>
+          <t xml:space="preserve">311865671</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
@@ -16111,7 +16111,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenkildevej 47</t>
+          <t xml:space="preserve">Rosenkildevej 57</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -16126,11 +16126,11 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H269">
-        <v>882</v>
+        <v>648</v>
       </c>
       <c r="I269" t="inlineStr">
         <is>
@@ -16171,7 +16171,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skanderborgvej 1</t>
+          <t xml:space="preserve">Rosenkildevej 61</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -16186,11 +16186,11 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="H270">
-        <v>805</v>
+        <v>677</v>
       </c>
       <c r="I270" t="inlineStr">
         <is>
@@ -16231,7 +16231,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenkildevej 61</t>
+          <t xml:space="preserve">Rosenkildevej 63</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -16246,11 +16246,11 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="H271">
-        <v>677</v>
+        <v>693</v>
       </c>
       <c r="I271" t="inlineStr">
         <is>
@@ -16291,7 +16291,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenkildevej 63</t>
+          <t xml:space="preserve">Rosenkildevej 65</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -16306,7 +16306,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="H272">
@@ -16351,7 +16351,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenkildevej 65</t>
+          <t xml:space="preserve">Rosenkildevej 67</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -16366,7 +16366,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="H273">
@@ -16411,7 +16411,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenkildevej 67</t>
+          <t xml:space="preserve">Rosenkildevej 69</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -16426,7 +16426,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="H274">
@@ -16471,7 +16471,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenkildevej 69</t>
+          <t xml:space="preserve">Rosenkildevej 71</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -16486,11 +16486,11 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="H275">
-        <v>693</v>
+        <v>528</v>
       </c>
       <c r="I275" t="inlineStr">
         <is>
@@ -16531,7 +16531,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenkildevej 71</t>
+          <t xml:space="preserve">Rosenkildevej 73</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -16546,11 +16546,11 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="H276">
-        <v>528</v>
+        <v>731</v>
       </c>
       <c r="I276" t="inlineStr">
         <is>
@@ -16591,7 +16591,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenkildevej 73</t>
+          <t xml:space="preserve">Rosenkildevej 75</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -16606,11 +16606,11 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="H277">
-        <v>731</v>
+        <v>714</v>
       </c>
       <c r="I277" t="inlineStr">
         <is>
@@ -16651,7 +16651,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenkildevej 75</t>
+          <t xml:space="preserve">Rosenkildevej 77</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -16666,11 +16666,11 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="H278">
-        <v>714</v>
+        <v>697</v>
       </c>
       <c r="I278" t="inlineStr">
         <is>
@@ -16711,7 +16711,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenkildevej 77</t>
+          <t xml:space="preserve">Rosenkildevej 79</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -16726,11 +16726,11 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="H279">
-        <v>697</v>
+        <v>692</v>
       </c>
       <c r="I279" t="inlineStr">
         <is>
@@ -16771,7 +16771,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenkildevej 79</t>
+          <t xml:space="preserve">Rosenkildevej 83A</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -16786,11 +16786,11 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="H280">
-        <v>692</v>
+        <v>4912</v>
       </c>
       <c r="I280" t="inlineStr">
         <is>
@@ -16831,7 +16831,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenkildevej 83A</t>
+          <t xml:space="preserve">Rosenkildevej 85</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -16846,11 +16846,11 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">29</t>
         </is>
       </c>
       <c r="H281">
-        <v>4912</v>
+        <v>2501</v>
       </c>
       <c r="I281" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenkildevej 85</t>
+          <t xml:space="preserve">Rosenkildevej 91A</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -16906,11 +16906,11 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t xml:space="preserve">29</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H282">
-        <v>2501</v>
+        <v>296</v>
       </c>
       <c r="I282" t="inlineStr">
         <is>
@@ -16951,7 +16951,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t xml:space="preserve">Æblehaven 2</t>
+          <t xml:space="preserve">Skanderborgvej 1</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -16966,11 +16966,11 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="H283">
-        <v>1552</v>
+        <v>805</v>
       </c>
       <c r="I283" t="inlineStr">
         <is>
@@ -17011,30 +17011,30 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenkildevej 57</t>
+          <t xml:space="preserve">Søbatteriet 17</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440066</t>
+          <t xml:space="preserve">5353038</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H284">
-        <v>648</v>
+        <v>842</v>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t xml:space="preserve">311865671</t>
+          <t xml:space="preserve">311865606</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
@@ -17071,7 +17071,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenkildevej 91A</t>
+          <t xml:space="preserve">Æblehaven 2</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -17086,11 +17086,11 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H285">
-        <v>296</v>
+        <v>1552</v>
       </c>
       <c r="I285" t="inlineStr">
         <is>
@@ -17191,30 +17191,30 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søbatteriet 3</t>
+          <t xml:space="preserve">Rosenkildevej 51</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t xml:space="preserve">9065073</t>
+          <t xml:space="preserve">9440066</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H287">
-        <v>364</v>
+        <v>278</v>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866935</t>
+          <t xml:space="preserve">311866933</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
@@ -17251,30 +17251,30 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenkildevej 51</t>
+          <t xml:space="preserve">Søbatteriet 3</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4220</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440066</t>
+          <t xml:space="preserve">9065073</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H288">
-        <v>278</v>
+        <v>364</v>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866933</t>
+          <t xml:space="preserve">311866935</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
@@ -17814,7 +17814,7 @@
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t xml:space="preserve">311876511</t>
+          <t xml:space="preserve">311876651</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
@@ -17874,7 +17874,7 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t xml:space="preserve">311876511</t>
+          <t xml:space="preserve">311876582</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">

--- a/public/exports/29188505.xlsx
+++ b/public/exports/29188505.xlsx
@@ -7014,7 +7014,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311531549</t>
+          <t xml:space="preserve">311531554</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">

--- a/public/exports/29188505.xlsx
+++ b/public/exports/29188505.xlsx
@@ -2394,7 +2394,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311313201</t>
+          <t xml:space="preserve">311313184</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311525861</t>
+          <t xml:space="preserve">311525853</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547265</t>
+          <t xml:space="preserve">311547262</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547259</t>
+          <t xml:space="preserve">311547262</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -8814,7 +8814,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547259</t>
+          <t xml:space="preserve">311547262</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547259</t>
+          <t xml:space="preserve">311547262</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547259</t>
+          <t xml:space="preserve">311547262</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -8994,7 +8994,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547259</t>
+          <t xml:space="preserve">311547262</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -9414,7 +9414,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547982</t>
+          <t xml:space="preserve">311547930</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -10734,7 +10734,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558846</t>
+          <t xml:space="preserve">311558842</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558830</t>
+          <t xml:space="preserve">311558842</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -11274,7 +11274,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560225</t>
+          <t xml:space="preserve">311560219</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -11454,7 +11454,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562131</t>
+          <t xml:space="preserve">311562133</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -11514,7 +11514,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562138</t>
+          <t xml:space="preserve">311562133</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -11874,7 +11874,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311566478</t>
+          <t xml:space="preserve">311566473</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -12414,7 +12414,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311569765</t>
+          <t xml:space="preserve">311569779</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -12774,7 +12774,7 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311571124</t>
+          <t xml:space="preserve">311571117</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -12834,7 +12834,7 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311571120</t>
+          <t xml:space="preserve">311571117</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
@@ -13554,7 +13554,7 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t xml:space="preserve">311577742</t>
+          <t xml:space="preserve">311577779</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -17394,7 +17394,7 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868309</t>
+          <t xml:space="preserve">311868284</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
@@ -17874,7 +17874,7 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t xml:space="preserve">311876582</t>
+          <t xml:space="preserve">311876603</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">

--- a/public/exports/29188505.xlsx
+++ b/public/exports/29188505.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L301"/>
+  <dimension ref="A1:M301"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -244,10 +259,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -304,10 +324,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -364,10 +389,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -424,10 +454,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -484,10 +519,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -544,10 +584,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -604,10 +649,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -664,10 +714,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -724,10 +779,15 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -784,10 +844,15 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -844,10 +909,15 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -904,10 +974,15 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -964,10 +1039,15 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1024,10 +1104,15 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1084,10 +1169,15 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1144,10 +1234,15 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1204,10 +1299,15 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1264,10 +1364,15 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1324,10 +1429,15 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1384,10 +1494,15 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1444,10 +1559,15 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1504,10 +1624,15 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1564,10 +1689,15 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1624,10 +1754,15 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1684,10 +1819,15 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1744,10 +1884,15 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1804,10 +1949,15 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1864,10 +2014,15 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1924,10 +2079,15 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1984,10 +2144,15 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2044,10 +2209,15 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2104,10 +2274,15 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2159,15 +2334,20 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Slagelse)</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-01-20</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2219,15 +2399,20 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-29</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2274,20 +2459,25 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311313206</t>
+          <t xml:space="preserve">311313184</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-05-09</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2334,20 +2524,25 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311313207</t>
+          <t xml:space="preserve">311313184</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-05-09</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2399,15 +2594,20 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-05-09</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2459,15 +2659,20 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-05-11</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2519,15 +2724,20 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-06-28</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2579,15 +2789,20 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-06-28</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2639,15 +2854,20 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-06-28</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2699,15 +2919,20 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-08-10</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2759,15 +2984,20 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-08-10</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2819,15 +3049,20 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-08-20</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2879,15 +3114,20 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-08-20</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2939,15 +3179,20 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-09-07</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2999,15 +3244,20 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-09-08</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3059,15 +3309,20 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-09-09</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3119,15 +3374,20 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-09-14</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3179,15 +3439,20 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-09-16</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3239,15 +3504,20 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-09-16</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3299,15 +3569,20 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-09-23</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3359,15 +3634,20 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-09-28</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3419,15 +3699,20 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-09-29</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3479,15 +3764,20 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-09-30</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3539,15 +3829,20 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-10-14</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3599,15 +3894,20 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-10-15</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3659,15 +3959,20 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-10-15</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3719,15 +4024,20 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-10-16</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3779,15 +4089,20 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-10-16</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3839,15 +4154,20 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-10-16</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3899,15 +4219,20 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-11-09</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3959,15 +4284,20 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-03</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4019,15 +4349,20 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-03</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4079,15 +4414,20 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-06</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4139,15 +4479,20 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-21</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4199,15 +4544,20 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-01-08</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4259,15 +4609,20 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-01-13</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4319,15 +4674,20 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-01-13</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4379,15 +4739,20 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-01-13</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4439,15 +4804,20 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-01-15</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4499,15 +4869,20 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-01-25</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4559,15 +4934,20 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-01-25</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4619,15 +4999,20 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-01-28</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4679,15 +5064,20 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-01-28</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4739,15 +5129,20 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-02-01</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4799,15 +5194,20 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-02-03</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4859,15 +5259,20 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-02-08</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4919,15 +5324,20 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-02-22</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4979,15 +5389,20 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-05</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5039,15 +5454,20 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-08</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5099,15 +5519,20 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-08</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5159,15 +5584,20 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-08</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5219,15 +5649,20 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-08</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5279,15 +5714,20 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-18</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5339,15 +5779,20 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-19</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5399,15 +5844,20 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-19</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5459,15 +5909,20 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-19</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5519,15 +5974,20 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-23</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5579,15 +6039,20 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-24</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5639,15 +6104,20 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-25</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5699,15 +6169,20 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-25</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5759,15 +6234,20 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-26</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5819,15 +6299,20 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-29</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5879,15 +6364,20 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-29</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5939,15 +6429,20 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-29</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5999,15 +6494,20 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-30</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6059,15 +6559,20 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-05-12</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6119,15 +6624,20 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-05-14</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6179,15 +6689,20 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-05-17</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6239,15 +6754,20 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-05-17</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6299,15 +6819,20 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-05-25</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6359,15 +6884,20 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-05-26</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6419,15 +6949,20 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-05-28</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6479,15 +7014,20 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-06-04</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6539,15 +7079,20 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-06-07</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6599,15 +7144,20 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-06-14</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6659,15 +7209,20 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-06-14</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6719,15 +7274,20 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-06-15</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6779,15 +7339,20 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-06-21</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6839,15 +7404,20 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-06-21</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6899,15 +7469,20 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-06-24</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6959,15 +7534,20 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-06-28</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7019,15 +7599,20 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-06-28</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7079,15 +7664,20 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-06-28</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7139,15 +7729,20 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-06-30</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7199,15 +7794,20 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-06-30</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7259,15 +7859,20 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-06-30</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7319,15 +7924,20 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-06-30</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7379,15 +7989,20 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-07-01</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7439,15 +8054,20 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-07-01</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7499,15 +8119,20 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-05</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7559,15 +8184,20 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-06</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7619,15 +8249,20 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-06</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7679,15 +8314,20 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-09</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7739,15 +8379,20 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-09</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7799,15 +8444,20 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-09</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7859,15 +8509,20 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-09</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7919,15 +8574,20 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-10</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7979,15 +8639,20 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-11</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8039,15 +8704,20 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-12</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8099,15 +8769,20 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-19</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8159,15 +8834,20 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-20</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8219,15 +8899,20 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-24</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8279,15 +8964,20 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-27</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8339,15 +9029,20 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-30</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8399,15 +9094,20 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-30</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8459,15 +9159,20 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-30</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8519,15 +9224,20 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-31</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8579,15 +9289,20 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-31</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8639,15 +9354,20 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-09</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8694,20 +9414,25 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547262</t>
+          <t xml:space="preserve">311547259</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-10</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8754,20 +9479,25 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547262</t>
+          <t xml:space="preserve">311547259</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-10</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8814,20 +9544,25 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547262</t>
+          <t xml:space="preserve">311547259</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-10</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8874,20 +9609,25 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547262</t>
+          <t xml:space="preserve">311547259</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-10</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8934,20 +9674,25 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547262</t>
+          <t xml:space="preserve">311547259</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-10</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8994,20 +9739,25 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547262</t>
+          <t xml:space="preserve">311547259</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-10</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9059,15 +9809,20 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-10</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9119,15 +9874,20 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-10</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9179,15 +9939,20 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-13</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9239,15 +10004,20 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-13</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9299,15 +10069,20 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-13</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9359,15 +10134,20 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-13</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9414,20 +10194,25 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547930</t>
+          <t xml:space="preserve">311547982</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-14</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9479,15 +10264,20 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-15</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9539,15 +10329,20 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-16</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9599,15 +10394,20 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-22</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9659,15 +10459,20 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-23</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9719,15 +10524,20 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-27</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9779,15 +10589,20 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-27</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9839,15 +10654,20 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-27</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9899,15 +10719,20 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-27</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9959,15 +10784,20 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-27</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10019,15 +10849,20 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-27</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10079,15 +10914,20 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-27</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10139,15 +10979,20 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-27</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10199,15 +11044,20 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-27</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10259,15 +11109,20 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-28</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10319,15 +11174,20 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-28</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10379,15 +11239,20 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-30</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10439,15 +11304,20 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-10-11</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10499,15 +11369,20 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-10-11</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10559,15 +11434,20 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-10-19</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10619,15 +11499,20 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-10-20</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10679,15 +11564,20 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-10-29</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10739,15 +11629,20 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-01</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10799,15 +11694,20 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-01</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10859,15 +11759,20 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-01</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10919,15 +11824,20 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-01</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10979,15 +11889,20 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-01</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11039,15 +11954,20 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-02</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11099,15 +12019,20 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-02</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11159,15 +12084,20 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-03</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11219,15 +12149,20 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-03</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11274,20 +12209,25 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560219</t>
+          <t xml:space="preserve">311560289</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-08</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11339,15 +12279,20 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-11</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11399,15 +12344,20 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-11</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11459,15 +12409,20 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-16</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11519,15 +12474,20 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-16</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11579,15 +12539,20 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-29</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11639,15 +12604,20 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-29</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11699,15 +12669,20 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-29</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11759,15 +12734,20 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-29</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11819,15 +12799,20 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-30</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11879,15 +12864,20 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-07</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11939,15 +12929,20 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-07</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11999,15 +12994,20 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-07</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12059,15 +13059,20 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-13</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12114,20 +13119,25 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311569003</t>
+          <t xml:space="preserve">311569066</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-20</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12174,20 +13184,25 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568977</t>
+          <t xml:space="preserve">311569066</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-20</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12234,20 +13249,25 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568956</t>
+          <t xml:space="preserve">311569066</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-20</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12299,15 +13319,20 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-21</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12359,15 +13384,20 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-21</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12419,15 +13449,20 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-23</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12474,20 +13509,25 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311569773</t>
+          <t xml:space="preserve">311569779</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-23</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12539,15 +13579,20 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-23</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12599,15 +13644,20 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-23</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12659,15 +13709,20 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-03</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12719,15 +13774,20 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-05</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12774,20 +13834,25 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311571117</t>
+          <t xml:space="preserve">311571124</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-07</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12834,20 +13899,25 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311571117</t>
+          <t xml:space="preserve">311571124</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-07</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12899,15 +13969,20 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-12</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12959,15 +14034,20 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-12</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13019,15 +14099,20 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-12</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13079,15 +14164,20 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-12</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13139,15 +14229,20 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-17</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13199,15 +14294,20 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-20</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13259,15 +14359,20 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-21</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13319,15 +14424,20 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-21</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13379,15 +14489,20 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-21</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13439,15 +14554,20 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-21</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13499,15 +14619,20 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-24</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13554,20 +14679,25 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t xml:space="preserve">311577779</t>
+          <t xml:space="preserve">311577742</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-02-09</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13619,15 +14749,20 @@
       </c>
       <c r="J227" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-02-18</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13679,15 +14814,20 @@
       </c>
       <c r="J228" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-02-18</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13739,15 +14879,20 @@
       </c>
       <c r="J229" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-02-18</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13799,15 +14944,20 @@
       </c>
       <c r="J230" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-14</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13859,15 +15009,20 @@
       </c>
       <c r="J231" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13919,15 +15074,20 @@
       </c>
       <c r="J232" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-29</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13979,15 +15139,20 @@
       </c>
       <c r="J233" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-31</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14039,15 +15204,20 @@
       </c>
       <c r="J234" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-31</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14099,15 +15269,20 @@
       </c>
       <c r="J235" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-31</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14159,15 +15334,20 @@
       </c>
       <c r="J236" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-05-20</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14219,15 +15399,20 @@
       </c>
       <c r="J237" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-06-01</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14279,15 +15464,20 @@
       </c>
       <c r="J238" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-10-03</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14339,15 +15529,20 @@
       </c>
       <c r="J239" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-22</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14399,15 +15594,20 @@
       </c>
       <c r="J240" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-10</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14459,15 +15659,20 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-21</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14519,15 +15724,20 @@
       </c>
       <c r="J242" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-05-15</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14579,15 +15789,20 @@
       </c>
       <c r="J243" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-05-15</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14639,15 +15854,20 @@
       </c>
       <c r="J244" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-05-15</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14699,15 +15919,20 @@
       </c>
       <c r="J245" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-05-15</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14759,15 +15984,20 @@
       </c>
       <c r="J246" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-05-15</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14819,15 +16049,20 @@
       </c>
       <c r="J247" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-09-28</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14879,15 +16114,20 @@
       </c>
       <c r="J248" t="inlineStr">
         <is>
+          <t xml:space="preserve">Murbyg ApS</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-01</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14939,15 +16179,20 @@
       </c>
       <c r="J249" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-04</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14999,15 +16244,20 @@
       </c>
       <c r="J250" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-04</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15059,15 +16309,20 @@
       </c>
       <c r="J251" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-04</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15119,15 +16374,20 @@
       </c>
       <c r="J252" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-04</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15179,15 +16439,20 @@
       </c>
       <c r="J253" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-18</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15239,15 +16504,20 @@
       </c>
       <c r="J254" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-31</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15299,15 +16569,20 @@
       </c>
       <c r="J255" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-22</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15359,15 +16634,20 @@
       </c>
       <c r="J256" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-07-04</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15419,15 +16699,20 @@
       </c>
       <c r="J257" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-07-09</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15479,15 +16764,20 @@
       </c>
       <c r="J258" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-07-16</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15539,15 +16829,20 @@
       </c>
       <c r="J259" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-07-29</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15599,15 +16894,20 @@
       </c>
       <c r="J260" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-05</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15659,15 +16959,20 @@
       </c>
       <c r="J261" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-05</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15719,15 +17024,20 @@
       </c>
       <c r="J262" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-05</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15779,15 +17089,20 @@
       </c>
       <c r="J263" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-05</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15839,15 +17154,20 @@
       </c>
       <c r="J264" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-08</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15899,15 +17219,20 @@
       </c>
       <c r="J265" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-08</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15959,15 +17284,20 @@
       </c>
       <c r="J266" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-17</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16019,15 +17349,20 @@
       </c>
       <c r="J267" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-31</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16079,15 +17414,20 @@
       </c>
       <c r="J268" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-31</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16139,15 +17479,20 @@
       </c>
       <c r="J269" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-31</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16199,15 +17544,20 @@
       </c>
       <c r="J270" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-31</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16259,15 +17609,20 @@
       </c>
       <c r="J271" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-31</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16319,15 +17674,20 @@
       </c>
       <c r="J272" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-31</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16379,15 +17739,20 @@
       </c>
       <c r="J273" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-31</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16439,15 +17804,20 @@
       </c>
       <c r="J274" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-31</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16499,15 +17869,20 @@
       </c>
       <c r="J275" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-31</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16559,15 +17934,20 @@
       </c>
       <c r="J276" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-31</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L276" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16619,15 +17999,20 @@
       </c>
       <c r="J277" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-31</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L277" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16679,15 +18064,20 @@
       </c>
       <c r="J278" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-31</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L278" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16739,15 +18129,20 @@
       </c>
       <c r="J279" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-31</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L279" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16799,15 +18194,20 @@
       </c>
       <c r="J280" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-31</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16859,15 +18259,20 @@
       </c>
       <c r="J281" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-31</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L281" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16919,15 +18324,20 @@
       </c>
       <c r="J282" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-31</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16979,15 +18389,20 @@
       </c>
       <c r="J283" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-31</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17039,15 +18454,20 @@
       </c>
       <c r="J284" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-31</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17099,15 +18519,20 @@
       </c>
       <c r="J285" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-31</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17159,15 +18584,20 @@
       </c>
       <c r="J286" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-05</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17219,15 +18649,20 @@
       </c>
       <c r="J287" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-07</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L287" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17279,15 +18714,20 @@
       </c>
       <c r="J288" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-07</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17339,15 +18779,20 @@
       </c>
       <c r="J289" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-12</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L289" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17394,20 +18839,25 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868284</t>
+          <t xml:space="preserve">311868309</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-14</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L290" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17459,15 +18909,20 @@
       </c>
       <c r="J291" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-28</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L291" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17519,15 +18974,20 @@
       </c>
       <c r="J292" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-02</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M292" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17579,15 +19039,20 @@
       </c>
       <c r="J293" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-02</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M293" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17639,15 +19104,20 @@
       </c>
       <c r="J294" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-03</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M294" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17699,15 +19169,20 @@
       </c>
       <c r="J295" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-05</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M295" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17759,15 +19234,20 @@
       </c>
       <c r="J296" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-18</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M296" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17814,20 +19294,25 @@
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t xml:space="preserve">311876651</t>
+          <t xml:space="preserve">311876511</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-14</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M297" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17874,20 +19359,25 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t xml:space="preserve">311876603</t>
+          <t xml:space="preserve">311876511</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-14</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M298" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17939,15 +19429,20 @@
       </c>
       <c r="J299" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-08</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L299" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M299" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17999,15 +19494,20 @@
       </c>
       <c r="J300" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-08</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L300" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M300" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18059,21 +19559,26 @@
       </c>
       <c r="J301" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-08</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L301" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L301"/>
+  <autoFilter ref="A1:M301"/>
 </worksheet>
 </file>
--- a/public/exports/29188505.xlsx
+++ b/public/exports/29188505.xlsx
@@ -5254,7 +5254,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311493661</t>
+          <t xml:space="preserve">311493572</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -7074,7 +7074,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311525853</t>
+          <t xml:space="preserve">311525848</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311531554</t>
+          <t xml:space="preserve">311531549</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -10194,7 +10194,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547982</t>
+          <t xml:space="preserve">311547930</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558842</t>
+          <t xml:space="preserve">311558830</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -12209,7 +12209,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560289</t>
+          <t xml:space="preserve">311560219</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -12404,12 +12404,12 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562133</t>
+          <t xml:space="preserve">311562131</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311569066</t>
+          <t xml:space="preserve">311569003</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -13184,7 +13184,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311569066</t>
+          <t xml:space="preserve">311568977</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -13249,7 +13249,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311569066</t>
+          <t xml:space="preserve">311568956</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -13444,7 +13444,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311569779</t>
+          <t xml:space="preserve">311569765</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -13509,7 +13509,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311569779</t>
+          <t xml:space="preserve">311569773</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -13639,7 +13639,7 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311569852</t>
+          <t xml:space="preserve">311569796</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
@@ -13834,7 +13834,7 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311571124</t>
+          <t xml:space="preserve">311571117</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -13899,7 +13899,7 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311571124</t>
+          <t xml:space="preserve">311571117</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
@@ -14094,7 +14094,7 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311571952</t>
+          <t xml:space="preserve">311571924</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
@@ -18839,7 +18839,7 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868309</t>
+          <t xml:space="preserve">311868284</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
